--- a/excel-dashboard-demo/output/dashboard_sample_ru.xlsx
+++ b/excel-dashboard-demo/output/dashboard_sample_ru.xlsx
@@ -30,6 +30,7 @@
     <definedName name="selTo">'Настройки'!$C$8</definedName>
     <definedName name="tgtAvail">'Настройки'!$C$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Дашборд'!$A$1:$R$67</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Журнал загрузки'!$B$12:$D$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -349,7 +350,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1990,9 +1993,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="4">
+      <c r="B3" s="4" t="str">
         <f>filterCaption</f>
-        <v/>
+        <v>Смена: Все   ·   Цех: Все   ·   Период: 01.09.2026 – 30.09.2026</v>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
@@ -2044,27 +2047,27 @@
     <row r="6">
       <c r="B6" s="8">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>2881.2</v>
       </c>
       <c r="D6" s="8">
         <f>SUMIFS(tblData[ПростойМин],tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>414.8333333333333</v>
       </c>
       <c r="F6" s="9">
         <f>IF(B6+D6=0,"",B6/(B6+D6))</f>
-        <v/>
+        <v>0.8741416450076354</v>
       </c>
       <c r="J6" s="10">
         <f>COUNTIFS(tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>412</v>
       </c>
       <c r="M6" s="10">
         <f>COUNTIFS(tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
-      </c>
-      <c r="P6" s="11">
+        <v>256</v>
+      </c>
+      <c r="P6" s="11" t="str">
         <f>IF('Простои'!$C$23="","–",'Простои'!$C$23)</f>
-        <v/>
+        <v>Поломка</v>
       </c>
     </row>
     <row r="7"/>
@@ -2081,9 +2084,9 @@
         </is>
       </c>
       <c r="E8" s="13" t="n"/>
-      <c r="F8" s="14">
+      <c r="F8" s="14" t="str">
         <f>IF(F6="","",IF(F6&gt;=tgtAvail,"▲ ","▼ ")&amp;"цель "&amp;ROUND(tgtAvail*100,1)&amp;"%")</f>
-        <v/>
+        <v>▲ цель 85%</v>
       </c>
       <c r="G8" s="13" t="n"/>
       <c r="J8" s="12" t="inlineStr">
@@ -2160,23 +2163,23 @@
       </c>
       <c r="C12" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Цех],$B12,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>1389.9</v>
       </c>
       <c r="D12" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Цех],$B12,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>218.16666666666666</v>
       </c>
       <c r="E12" s="20">
         <f>IF(C12+D12=0,"",C12/(C12+D12))</f>
-        <v/>
+        <v>0.8643298370714315</v>
       </c>
       <c r="F12" s="21">
         <f>COUNTIFS(tblData[Цех],$B12,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>201</v>
       </c>
       <c r="G12" s="20">
         <f>IF($D$16=0,0,D12/$D$16)</f>
-        <v/>
+        <v>0.52591402169546</v>
       </c>
     </row>
     <row r="13">
@@ -2187,23 +2190,23 @@
       </c>
       <c r="C13" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Цех],$B13,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="D13" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Цех],$B13,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="E13" s="20">
         <f>IF(C13+D13=0,"",C13/(C13+D13))</f>
-        <v/>
+        <v>0.9134615384615384</v>
       </c>
       <c r="F13" s="21">
         <f>COUNTIFS(tblData[Цех],$B13,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="G13" s="20">
         <f>IF($D$16=0,0,D13/$D$16)</f>
-        <v/>
+        <v>0.043390920048212135</v>
       </c>
     </row>
     <row r="14">
@@ -2214,23 +2217,23 @@
       </c>
       <c r="C14" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Цех],$B14,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>651.81</v>
       </c>
       <c r="D14" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Цех],$B14,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>84.16666666666667</v>
       </c>
       <c r="E14" s="20">
         <f>IF(C14+D14=0,"",C14/(C14+D14))</f>
-        <v/>
+        <v>0.8856394903823944</v>
       </c>
       <c r="F14" s="21">
         <f>COUNTIFS(tblData[Цех],$B14,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>92</v>
       </c>
       <c r="G14" s="20">
         <f>IF($D$16=0,0,D14/$D$16)</f>
-        <v/>
+        <v>0.20289272800321417</v>
       </c>
     </row>
     <row r="15">
@@ -2241,23 +2244,23 @@
       </c>
       <c r="C15" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Цех],$B15,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>649.49</v>
       </c>
       <c r="D15" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Цех],$B15,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>94.5</v>
       </c>
       <c r="E15" s="20">
         <f>IF(C15+D15=0,"",C15/(C15+D15))</f>
-        <v/>
+        <v>0.8729821637387599</v>
       </c>
       <c r="F15" s="21">
         <f>COUNTIFS(tblData[Цех],$B15,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>93</v>
       </c>
       <c r="G15" s="20">
         <f>IF($D$16=0,0,D15/$D$16)</f>
-        <v/>
+        <v>0.22780233025311372</v>
       </c>
     </row>
     <row r="16">
@@ -2268,23 +2271,23 @@
       </c>
       <c r="C16" s="23">
         <f>SUM(C12:C15)</f>
-        <v/>
+        <v>2881.2</v>
       </c>
       <c r="D16" s="23">
         <f>SUM(D12:D15)</f>
-        <v/>
+        <v>414.8333333333333</v>
       </c>
       <c r="E16" s="24">
         <f>IF(C16+D16=0,"",C16/(C16+D16))</f>
-        <v/>
+        <v>0.8741416450076354</v>
       </c>
       <c r="F16" s="25">
         <f>SUM(F12:F15)</f>
-        <v/>
+        <v>412</v>
       </c>
       <c r="G16" s="24">
         <f>IF(D16=0,0,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2339,23 +2342,23 @@
       </c>
       <c r="C28" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Оборудование],$B28,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>331.74</v>
       </c>
       <c r="D28" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B28,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>44.25</v>
       </c>
       <c r="E28" s="20">
         <f>IF(C28+D28=0,"",C28/(C28+D28))</f>
-        <v/>
+        <v>0.882310699752653</v>
       </c>
       <c r="F28" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B28,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>47</v>
       </c>
       <c r="G28" s="20">
         <f>IF($D$36=0,0,D28/$D$36)</f>
-        <v/>
+        <v>0.1066693451185215</v>
       </c>
     </row>
     <row r="29">
@@ -2366,23 +2369,23 @@
       </c>
       <c r="C29" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Оборудование],$B29,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>320.07</v>
       </c>
       <c r="D29" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B29,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>39.916666666666664</v>
       </c>
       <c r="E29" s="20">
         <f>IF(C29+D29=0,"",C29/(C29+D29))</f>
-        <v/>
+        <v>0.8891162635653171</v>
       </c>
       <c r="F29" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B29,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="G29" s="20">
         <f>IF($D$36=0,0,D29/$D$36)</f>
-        <v/>
+        <v>0.09622338288469265</v>
       </c>
     </row>
     <row r="30">
@@ -2393,23 +2396,23 @@
       </c>
       <c r="C30" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Оборудование],$B30,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>447.43</v>
       </c>
       <c r="D30" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B30,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>72.58333333333333</v>
       </c>
       <c r="E30" s="20">
         <f>IF(C30+D30=0,"",C30/(C30+D30))</f>
-        <v/>
+        <v>0.8604202456347273</v>
       </c>
       <c r="F30" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B30,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>65</v>
       </c>
       <c r="G30" s="20">
         <f>IF($D$36=0,0,D30/$D$36)</f>
-        <v/>
+        <v>0.17496986741663317</v>
       </c>
     </row>
     <row r="31">
@@ -2420,23 +2423,23 @@
       </c>
       <c r="C31" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Оборудование],$B31,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>460.45</v>
       </c>
       <c r="D31" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B31,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>91.58333333333333</v>
       </c>
       <c r="E31" s="20">
         <f>IF(C31+D31=0,"",C31/(C31+D31))</f>
-        <v/>
+        <v>0.8340981824769036</v>
       </c>
       <c r="F31" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B31,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>69</v>
       </c>
       <c r="G31" s="20">
         <f>IF($D$36=0,0,D31/$D$36)</f>
-        <v/>
+        <v>0.22077139413419045</v>
       </c>
     </row>
     <row r="32">
@@ -2447,23 +2450,23 @@
       </c>
       <c r="C32" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Оборудование],$B32,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>482.02</v>
       </c>
       <c r="D32" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B32,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>54</v>
       </c>
       <c r="E32" s="20">
         <f>IF(C32+D32=0,"",C32/(C32+D32))</f>
-        <v/>
+        <v>0.8992574903921495</v>
       </c>
       <c r="F32" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B32,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>67</v>
       </c>
       <c r="G32" s="20">
         <f>IF($D$36=0,0,D32/$D$36)</f>
-        <v/>
+        <v>0.1301727601446364</v>
       </c>
     </row>
     <row r="33">
@@ -2474,23 +2477,23 @@
       </c>
       <c r="C33" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Оборудование],$B33,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="D33" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B33,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="E33" s="20">
         <f>IF(C33+D33=0,"",C33/(C33+D33))</f>
-        <v/>
+        <v>0.9134615384615384</v>
       </c>
       <c r="F33" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B33,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="G33" s="20">
         <f>IF($D$36=0,0,D33/$D$36)</f>
-        <v/>
+        <v>0.043390920048212135</v>
       </c>
     </row>
     <row r="34">
@@ -2501,23 +2504,23 @@
       </c>
       <c r="C34" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Оборудование],$B34,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>331.08</v>
       </c>
       <c r="D34" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B34,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>44.916666666666664</v>
       </c>
       <c r="E34" s="20">
         <f>IF(C34+D34=0,"",C34/(C34+D34))</f>
-        <v/>
+        <v>0.8805397210968182</v>
       </c>
       <c r="F34" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B34,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>47</v>
       </c>
       <c r="G34" s="20">
         <f>IF($D$36=0,0,D34/$D$36)</f>
-        <v/>
+        <v>0.10827641623141825</v>
       </c>
     </row>
     <row r="35">
@@ -2528,23 +2531,23 @@
       </c>
       <c r="C35" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Оборудование],$B35,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>318.41</v>
       </c>
       <c r="D35" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B35,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>49.583333333333336</v>
       </c>
       <c r="E35" s="20">
         <f>IF(C35+D35=0,"",C35/(C35+D35))</f>
-        <v/>
+        <v>0.8652602402217432</v>
       </c>
       <c r="F35" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B35,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="G35" s="20">
         <f>IF($D$36=0,0,D35/$D$36)</f>
-        <v/>
+        <v>0.11952591402169548</v>
       </c>
     </row>
     <row r="36">
@@ -2555,23 +2558,23 @@
       </c>
       <c r="C36" s="23">
         <f>SUM(C28:C35)</f>
-        <v/>
+        <v>2881.2</v>
       </c>
       <c r="D36" s="23">
         <f>SUM(D28:D35)</f>
-        <v/>
+        <v>414.8333333333333</v>
       </c>
       <c r="E36" s="24">
         <f>IF(C36+D36=0,"",C36/(C36+D36))</f>
-        <v/>
+        <v>0.8741416450076354</v>
       </c>
       <c r="F36" s="25">
         <f>SUM(F28:F35)</f>
-        <v/>
+        <v>412</v>
       </c>
       <c r="G36" s="24">
         <f>IF(D36=0,0,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2626,23 +2629,23 @@
       </c>
       <c r="C44" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B44,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>143.57</v>
       </c>
       <c r="D44" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B44,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>24.416666666666668</v>
       </c>
       <c r="E44" s="20">
         <f>IF(C44+D44=0,"",C44/(C44+D44))</f>
-        <v/>
+        <v>0.8546511627906977</v>
       </c>
       <c r="F44" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B44,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="G44" s="20">
         <f>IF($D$62=0,0,D44/$D$62)</f>
-        <v/>
+        <v>0.058858979509843305</v>
       </c>
     </row>
     <row r="45">
@@ -2653,23 +2656,23 @@
       </c>
       <c r="C45" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B45,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>176.82</v>
       </c>
       <c r="D45" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B45,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>31.166666666666668</v>
       </c>
       <c r="E45" s="20">
         <f>IF(C45+D45=0,"",C45/(C45+D45))</f>
-        <v/>
+        <v>0.8501506506827361</v>
       </c>
       <c r="F45" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B45,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="G45" s="20">
         <f>IF($D$62=0,0,D45/$D$62)</f>
-        <v/>
+        <v>0.07513057452792285</v>
       </c>
     </row>
     <row r="46">
@@ -2680,23 +2683,23 @@
       </c>
       <c r="C46" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B46,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>141.09</v>
       </c>
       <c r="D46" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B46,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>18.916666666666668</v>
       </c>
       <c r="E46" s="20">
         <f>IF(C46+D46=0,"",C46/(C46+D46))</f>
-        <v/>
+        <v>0.8817757593433607</v>
       </c>
       <c r="F46" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B46,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="G46" s="20">
         <f>IF($D$62=0,0,D46/$D$62)</f>
-        <v/>
+        <v>0.045600642828445156</v>
       </c>
     </row>
     <row r="47">
@@ -2707,23 +2710,23 @@
       </c>
       <c r="C47" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B47,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>145.75</v>
       </c>
       <c r="D47" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B47,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>22.25</v>
       </c>
       <c r="E47" s="20">
         <f>IF(C47+D47=0,"",C47/(C47+D47))</f>
-        <v/>
+        <v>0.8675595238095238</v>
       </c>
       <c r="F47" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B47,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="G47" s="20">
         <f>IF($D$62=0,0,D47/$D$62)</f>
-        <v/>
+        <v>0.05363599839292888</v>
       </c>
     </row>
     <row r="48">
@@ -2734,23 +2737,23 @@
       </c>
       <c r="C48" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>154.92</v>
       </c>
       <c r="D48" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>13.083333333333334</v>
       </c>
       <c r="E48" s="20">
         <f>IF(C48+D48=0,"",C48/(C48+D48))</f>
-        <v/>
+        <v>0.9221245610206146</v>
       </c>
       <c r="F48" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="G48" s="20">
         <f>IF($D$62=0,0,D48/$D$62)</f>
-        <v/>
+        <v>0.03153877059059863</v>
       </c>
     </row>
     <row r="49">
@@ -2761,23 +2764,23 @@
       </c>
       <c r="C49" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B49,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>176.09</v>
       </c>
       <c r="D49" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B49,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>23.916666666666668</v>
       </c>
       <c r="E49" s="20">
         <f>IF(C49+D49=0,"",C49/(C49+D49))</f>
-        <v/>
+        <v>0.8804206526449119</v>
       </c>
       <c r="F49" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B49,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="G49" s="20">
         <f>IF($D$62=0,0,D49/$D$62)</f>
-        <v/>
+        <v>0.05765367617517075</v>
       </c>
     </row>
     <row r="50">
@@ -2788,23 +2791,23 @@
       </c>
       <c r="C50" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B50,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>165.85</v>
       </c>
       <c r="D50" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B50,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>26.166666666666668</v>
       </c>
       <c r="E50" s="20">
         <f>IF(C50+D50=0,"",C50/(C50+D50))</f>
-        <v/>
+        <v>0.86372710702196</v>
       </c>
       <c r="F50" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B50,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="G50" s="20">
         <f>IF($D$62=0,0,D50/$D$62)</f>
-        <v/>
+        <v>0.06307754118119727</v>
       </c>
     </row>
     <row r="51">
@@ -2815,23 +2818,23 @@
       </c>
       <c r="C51" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B51,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>151.27</v>
       </c>
       <c r="D51" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B51,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>24.75</v>
       </c>
       <c r="E51" s="20">
         <f>IF(C51+D51=0,"",C51/(C51+D51))</f>
-        <v/>
+        <v>0.8593909782979207</v>
       </c>
       <c r="F51" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B51,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="G51" s="20">
         <f>IF($D$62=0,0,D51/$D$62)</f>
-        <v/>
+        <v>0.05966251506629168</v>
       </c>
     </row>
     <row r="52">
@@ -2842,23 +2845,23 @@
       </c>
       <c r="C52" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B52,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>164.51</v>
       </c>
       <c r="D52" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B52,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>35.5</v>
       </c>
       <c r="E52" s="20">
         <f>IF(C52+D52=0,"",C52/(C52+D52))</f>
-        <v/>
+        <v>0.8225088745562722</v>
       </c>
       <c r="F52" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B52,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="G52" s="20">
         <f>IF($D$62=0,0,D52/$D$62)</f>
-        <v/>
+        <v>0.0855765367617517</v>
       </c>
     </row>
     <row r="53">
@@ -2869,23 +2872,23 @@
       </c>
       <c r="C53" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B53,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>187.18</v>
       </c>
       <c r="D53" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B53,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>12.833333333333334</v>
       </c>
       <c r="E53" s="20">
         <f>IF(C53+D53=0,"",C53/(C53+D53))</f>
-        <v/>
+        <v>0.9358376108259449</v>
       </c>
       <c r="F53" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B53,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="G53" s="20">
         <f>IF($D$62=0,0,D53/$D$62)</f>
-        <v/>
+        <v>0.030936118923262354</v>
       </c>
     </row>
     <row r="54">
@@ -2896,23 +2899,23 @@
       </c>
       <c r="C54" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B54,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>174.32</v>
       </c>
       <c r="D54" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B54,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>17.666666666666668</v>
       </c>
       <c r="E54" s="20">
         <f>IF(C54+D54=0,"",C54/(C54+D54))</f>
-        <v/>
+        <v>0.9079797208139454</v>
       </c>
       <c r="F54" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B54,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="G54" s="20">
         <f>IF($D$62=0,0,D54/$D$62)</f>
-        <v/>
+        <v>0.04258738449176376</v>
       </c>
     </row>
     <row r="55">
@@ -2923,23 +2926,23 @@
       </c>
       <c r="C55" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B55,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>142.32</v>
       </c>
       <c r="D55" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B55,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>25.666666666666668</v>
       </c>
       <c r="E55" s="20">
         <f>IF(C55+D55=0,"",C55/(C55+D55))</f>
-        <v/>
+        <v>0.8472100960393683</v>
       </c>
       <c r="F55" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B55,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="G55" s="20">
         <f>IF($D$62=0,0,D55/$D$62)</f>
-        <v/>
+        <v>0.06187223784652471</v>
       </c>
     </row>
     <row r="56">
@@ -2950,23 +2953,23 @@
       </c>
       <c r="C56" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B56,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>153.75</v>
       </c>
       <c r="D56" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B56,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>22.25</v>
       </c>
       <c r="E56" s="20">
         <f>IF(C56+D56=0,"",C56/(C56+D56))</f>
-        <v/>
+        <v>0.8735795454545454</v>
       </c>
       <c r="F56" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B56,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="G56" s="20">
         <f>IF($D$62=0,0,D56/$D$62)</f>
-        <v/>
+        <v>0.05363599839292888</v>
       </c>
     </row>
     <row r="57">
@@ -2977,23 +2980,23 @@
       </c>
       <c r="C57" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B57,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>144.67</v>
       </c>
       <c r="D57" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B57,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>31.333333333333332</v>
       </c>
       <c r="E57" s="20">
         <f>IF(C57+D57=0,"",C57/(C57+D57))</f>
-        <v/>
+        <v>0.8219730686918808</v>
       </c>
       <c r="F57" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B57,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="G57" s="20">
         <f>IF($D$62=0,0,D57/$D$62)</f>
-        <v/>
+        <v>0.07553234230614704</v>
       </c>
     </row>
     <row r="58">
@@ -3004,23 +3007,23 @@
       </c>
       <c r="C58" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B58,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>190</v>
       </c>
       <c r="D58" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B58,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="E58" s="20">
         <f>IF(C58+D58=0,"",C58/(C58+D58))</f>
-        <v/>
+        <v>0.9134615384615384</v>
       </c>
       <c r="F58" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B58,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>26</v>
       </c>
       <c r="G58" s="20">
         <f>IF($D$62=0,0,D58/$D$62)</f>
-        <v/>
+        <v>0.04339092004821213</v>
       </c>
     </row>
     <row r="59">
@@ -3031,23 +3034,23 @@
       </c>
       <c r="C59" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B59,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>158.58</v>
       </c>
       <c r="D59" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B59,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>17.416666666666668</v>
       </c>
       <c r="E59" s="20">
         <f>IF(C59+D59=0,"",C59/(C59+D59))</f>
-        <v/>
+        <v>0.9010397924203111</v>
       </c>
       <c r="F59" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B59,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="G59" s="20">
         <f>IF($D$62=0,0,D59/$D$62)</f>
-        <v/>
+        <v>0.04198473282442748</v>
       </c>
     </row>
     <row r="60">
@@ -3058,23 +3061,23 @@
       </c>
       <c r="C60" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B60,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>138.01</v>
       </c>
       <c r="D60" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B60,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>22</v>
       </c>
       <c r="E60" s="20">
         <f>IF(C60+D60=0,"",C60/(C60+D60))</f>
-        <v/>
+        <v>0.8625085932129242</v>
       </c>
       <c r="F60" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B60,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>20</v>
       </c>
       <c r="G60" s="20">
         <f>IF($D$62=0,0,D60/$D$62)</f>
-        <v/>
+        <v>0.0530333467255926</v>
       </c>
     </row>
     <row r="61">
@@ -3085,23 +3088,23 @@
       </c>
       <c r="C61" s="19">
         <f>SUMIFS(tblData[ЧасыРаботы],tblData[Сотрудник],$B61,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>172.5</v>
       </c>
       <c r="D61" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Сотрудник],$B61,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>27.5</v>
       </c>
       <c r="E61" s="20">
         <f>IF(C61+D61=0,"",C61/(C61+D61))</f>
-        <v/>
+        <v>0.8625</v>
       </c>
       <c r="F61" s="21">
         <f>COUNTIFS(tblData[Сотрудник],$B61,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>25</v>
       </c>
       <c r="G61" s="20">
         <f>IF($D$62=0,0,D61/$D$62)</f>
-        <v/>
+        <v>0.06629168340699075</v>
       </c>
     </row>
     <row r="62">
@@ -3112,23 +3115,23 @@
       </c>
       <c r="C62" s="23">
         <f>SUM(C44:C61)</f>
-        <v/>
+        <v>2881.2</v>
       </c>
       <c r="D62" s="23">
         <f>SUM(D44:D61)</f>
-        <v/>
+        <v>414.83333333333337</v>
       </c>
       <c r="E62" s="24">
         <f>IF(C62+D62=0,"",C62/(C62+D62))</f>
-        <v/>
+        <v>0.8741416450076354</v>
       </c>
       <c r="F62" s="25">
         <f>SUM(F44:F61)</f>
-        <v/>
+        <v>412</v>
       </c>
       <c r="G62" s="24">
         <f>IF(D62=0,0,1)</f>
-        <v/>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -3221,9 +3224,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="4">
+      <c r="B3" s="4" t="str">
         <f>filterCaption</f>
-        <v/>
+        <v>Смена: Все   ·   Цех: Все   ·   Период: 01.09.2026 – 30.09.2026</v>
       </c>
     </row>
     <row r="5">
@@ -3288,23 +3291,23 @@
       </c>
       <c r="D7" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B7,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>44.25</v>
       </c>
       <c r="E7" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B7,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="F7" s="21">
         <f>IF(E7=0,"",D7*60/E7)</f>
-        <v/>
+        <v>91.55172413793103</v>
       </c>
       <c r="G7" s="20">
         <f>IF($D$15=0,0,D7/$D$15)</f>
-        <v/>
-      </c>
-      <c r="H7" s="18">
+        <v>0.1066693451185215</v>
+      </c>
+      <c r="H7" s="18" t="str">
         <f>IF(MAX($C$49:$I$49)&lt;=0,"–",INDEX($C$48:$I$48,1,MATCH(MAX($C$49:$I$49),$C$49:$I$49,0)))</f>
-        <v/>
+        <v>Нет материала</v>
       </c>
     </row>
     <row r="8">
@@ -3320,23 +3323,23 @@
       </c>
       <c r="D8" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B8,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>39.916666666666664</v>
       </c>
       <c r="E8" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B8,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="F8" s="21">
         <f>IF(E8=0,"",D8*60/E8)</f>
-        <v/>
+        <v>99.79166666666667</v>
       </c>
       <c r="G8" s="20">
         <f>IF($D$15=0,0,D8/$D$15)</f>
-        <v/>
-      </c>
-      <c r="H8" s="18">
+        <v>0.09622338288469265</v>
+      </c>
+      <c r="H8" s="18" t="str">
         <f>IF(MAX($C$50:$I$50)&lt;=0,"–",INDEX($C$48:$I$48,1,MATCH(MAX($C$50:$I$50),$C$50:$I$50,0)))</f>
-        <v/>
+        <v>Переналадка</v>
       </c>
     </row>
     <row r="9">
@@ -3352,23 +3355,23 @@
       </c>
       <c r="D9" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B9,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>72.58333333333333</v>
       </c>
       <c r="E9" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B9,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="F9" s="21">
         <f>IF(E9=0,"",D9*60/E9)</f>
-        <v/>
+        <v>96.77777777777777</v>
       </c>
       <c r="G9" s="20">
         <f>IF($D$15=0,0,D9/$D$15)</f>
-        <v/>
-      </c>
-      <c r="H9" s="18">
+        <v>0.17496986741663317</v>
+      </c>
+      <c r="H9" s="18" t="str">
         <f>IF(MAX($C$51:$I$51)&lt;=0,"–",INDEX($C$48:$I$48,1,MATCH(MAX($C$51:$I$51),$C$51:$I$51,0)))</f>
-        <v/>
+        <v>Переналадка</v>
       </c>
     </row>
     <row r="10">
@@ -3384,23 +3387,23 @@
       </c>
       <c r="D10" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B10,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>91.58333333333333</v>
       </c>
       <c r="E10" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B10,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>56</v>
       </c>
       <c r="F10" s="21">
         <f>IF(E10=0,"",D10*60/E10)</f>
-        <v/>
+        <v>98.125</v>
       </c>
       <c r="G10" s="20">
         <f>IF($D$15=0,0,D10/$D$15)</f>
-        <v/>
-      </c>
-      <c r="H10" s="18">
+        <v>0.22077139413419045</v>
+      </c>
+      <c r="H10" s="18" t="str">
         <f>IF(MAX($C$52:$I$52)&lt;=0,"–",INDEX($C$48:$I$48,1,MATCH(MAX($C$52:$I$52),$C$52:$I$52,0)))</f>
-        <v/>
+        <v>Поломка</v>
       </c>
     </row>
     <row r="11">
@@ -3416,23 +3419,23 @@
       </c>
       <c r="D11" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B11,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>54</v>
       </c>
       <c r="E11" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B11,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>30</v>
       </c>
       <c r="F11" s="21">
         <f>IF(E11=0,"",D11*60/E11)</f>
-        <v/>
+        <v>108</v>
       </c>
       <c r="G11" s="20">
         <f>IF($D$15=0,0,D11/$D$15)</f>
-        <v/>
-      </c>
-      <c r="H11" s="18">
+        <v>0.1301727601446364</v>
+      </c>
+      <c r="H11" s="18" t="str">
         <f>IF(MAX($C$53:$I$53)&lt;=0,"–",INDEX($C$48:$I$48,1,MATCH(MAX($C$53:$I$53),$C$53:$I$53,0)))</f>
-        <v/>
+        <v>Поломка</v>
       </c>
     </row>
     <row r="12">
@@ -3448,23 +3451,23 @@
       </c>
       <c r="D12" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B12,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>18</v>
       </c>
       <c r="E12" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B12,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>15</v>
       </c>
       <c r="F12" s="21">
         <f>IF(E12=0,"",D12*60/E12)</f>
-        <v/>
+        <v>72</v>
       </c>
       <c r="G12" s="20">
         <f>IF($D$15=0,0,D12/$D$15)</f>
-        <v/>
-      </c>
-      <c r="H12" s="18">
+        <v>0.043390920048212135</v>
+      </c>
+      <c r="H12" s="18" t="str">
         <f>IF(MAX($C$54:$I$54)&lt;=0,"–",INDEX($C$48:$I$48,1,MATCH(MAX($C$54:$I$54),$C$54:$I$54,0)))</f>
-        <v/>
+        <v>Переналадка</v>
       </c>
     </row>
     <row r="13">
@@ -3480,23 +3483,23 @@
       </c>
       <c r="D13" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B13,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>44.916666666666664</v>
       </c>
       <c r="E13" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B13,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>28</v>
       </c>
       <c r="F13" s="21">
         <f>IF(E13=0,"",D13*60/E13)</f>
-        <v/>
+        <v>96.25</v>
       </c>
       <c r="G13" s="20">
         <f>IF($D$15=0,0,D13/$D$15)</f>
-        <v/>
-      </c>
-      <c r="H13" s="18">
+        <v>0.10827641623141825</v>
+      </c>
+      <c r="H13" s="18" t="str">
         <f>IF(MAX($C$55:$I$55)&lt;=0,"–",INDEX($C$48:$I$48,1,MATCH(MAX($C$55:$I$55),$C$55:$I$55,0)))</f>
-        <v/>
+        <v>Поломка</v>
       </c>
     </row>
     <row r="14">
@@ -3512,23 +3515,23 @@
       </c>
       <c r="D14" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B14,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>49.583333333333336</v>
       </c>
       <c r="E14" s="21">
         <f>COUNTIFS(tblData[Оборудование],$B14,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>29</v>
       </c>
       <c r="F14" s="21">
         <f>IF(E14=0,"",D14*60/E14)</f>
-        <v/>
+        <v>102.58620689655173</v>
       </c>
       <c r="G14" s="20">
         <f>IF($D$15=0,0,D14/$D$15)</f>
-        <v/>
-      </c>
-      <c r="H14" s="18">
+        <v>0.11952591402169548</v>
+      </c>
+      <c r="H14" s="18" t="str">
         <f>IF(MAX($C$56:$I$56)&lt;=0,"–",INDEX($C$48:$I$48,1,MATCH(MAX($C$56:$I$56),$C$56:$I$56,0)))</f>
-        <v/>
+        <v>Поломка</v>
       </c>
     </row>
     <row r="15">
@@ -3540,19 +3543,19 @@
       <c r="C15" s="27" t="n"/>
       <c r="D15" s="23">
         <f>SUM(D7:D14)</f>
-        <v/>
+        <v>414.8333333333333</v>
       </c>
       <c r="E15" s="25">
         <f>SUM(E7:E14)</f>
-        <v/>
+        <v>256</v>
       </c>
       <c r="F15" s="25">
         <f>IF(E15=0,"",D15*60/E15)</f>
-        <v/>
+        <v>97.2265625</v>
       </c>
       <c r="G15" s="24">
         <f>IF(D15=0,0,1)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="H15" s="27" t="n"/>
     </row>
@@ -3594,105 +3597,105 @@
       <c r="B23" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="C23" s="18">
+      <c r="C23" s="18" t="str">
         <f>IF(INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B23),$F$38:$F$44,0))&lt;=0,"",INDEX($B$38:$B$44,MATCH(LARGE($F$38:$F$44,$B23),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>Поломка</v>
       </c>
       <c r="D23" s="19">
         <f>IF(C23="","",INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B23),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>138.41666666666666</v>
       </c>
       <c r="E23" s="21">
         <f>IF(C23="","",INDEX($D$38:$D$44,MATCH(LARGE($F$38:$F$44,$B23),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="F23" s="20">
         <f>IF(C23="","",INDEX($E$38:$E$44,MATCH(LARGE($F$38:$F$44,$B23),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>0.33366813981518684</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="18" t="str">
         <f>IF(INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B24),$F$38:$F$44,0))&lt;=0,"",INDEX($B$38:$B$44,MATCH(LARGE($F$38:$F$44,$B24),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>Нет материала</v>
       </c>
       <c r="D24" s="19">
         <f>IF(C24="","",INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B24),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>97.5</v>
       </c>
       <c r="E24" s="21">
         <f>IF(C24="","",INDEX($D$38:$D$44,MATCH(LARGE($F$38:$F$44,$B24),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="F24" s="20">
         <f>IF(C24="","",INDEX($E$38:$E$44,MATCH(LARGE($F$38:$F$44,$B24),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>0.23503415026114907</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="C25" s="18">
+      <c r="C25" s="18" t="str">
         <f>IF(INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B25),$F$38:$F$44,0))&lt;=0,"",INDEX($B$38:$B$44,MATCH(LARGE($F$38:$F$44,$B25),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>Переналадка</v>
       </c>
       <c r="D25" s="19">
         <f>IF(C25="","",INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B25),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>88.66666666666667</v>
       </c>
       <c r="E25" s="21">
         <f>IF(C25="","",INDEX($D$38:$D$44,MATCH(LARGE($F$38:$F$44,$B25),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>78</v>
       </c>
       <c r="F25" s="20">
         <f>IF(C25="","",INDEX($E$38:$E$44,MATCH(LARGE($F$38:$F$44,$B25),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>0.2137404580152672</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="18" t="str">
         <f>IF(INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B26),$F$38:$F$44,0))&lt;=0,"",INDEX($B$38:$B$44,MATCH(LARGE($F$38:$F$44,$B26),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>Плановое ТО</v>
       </c>
       <c r="D26" s="19">
         <f>IF(C26="","",INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B26),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>46.5</v>
       </c>
       <c r="E26" s="21">
         <f>IF(C26="","",INDEX($D$38:$D$44,MATCH(LARGE($F$38:$F$44,$B26),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="F26" s="20">
         <f>IF(C26="","",INDEX($E$38:$E$44,MATCH(LARGE($F$38:$F$44,$B26),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>0.11209321012454801</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="28" t="n">
         <v>5</v>
       </c>
-      <c r="C27" s="18">
+      <c r="C27" s="18" t="str">
         <f>IF(INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B27),$F$38:$F$44,0))&lt;=0,"",INDEX($B$38:$B$44,MATCH(LARGE($F$38:$F$44,$B27),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>Контроль качества</v>
       </c>
       <c r="D27" s="19">
         <f>IF(C27="","",INDEX($C$38:$C$44,MATCH(LARGE($F$38:$F$44,$B27),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>22.416666666666668</v>
       </c>
       <c r="E27" s="21">
         <f>IF(C27="","",INDEX($D$38:$D$44,MATCH(LARGE($F$38:$F$44,$B27),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="F27" s="20">
         <f>IF(C27="","",INDEX($E$38:$E$44,MATCH(LARGE($F$38:$F$44,$B27),$F$38:$F$44,0)))</f>
-        <v/>
+        <v>0.05403776617115308</v>
       </c>
     </row>
     <row r="36">
@@ -3737,19 +3740,19 @@
       </c>
       <c r="C38" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[ПричинаПростоя],$B38,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>10.666666666666666</v>
       </c>
       <c r="D38" s="21">
         <f>COUNTIFS(tblData[ПричинаПростоя],$B38,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>23</v>
       </c>
       <c r="E38" s="20">
         <f>IF($C$45=0,0,C38/$C$45)</f>
-        <v/>
+        <v>0.02571313780634793</v>
       </c>
       <c r="F38" s="29">
         <f>C38+(10000-ROW())/100000000</f>
-        <v/>
+        <v>10.666766286666666</v>
       </c>
     </row>
     <row r="39">
@@ -3760,19 +3763,19 @@
       </c>
       <c r="C39" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[ПричинаПростоя],$B39,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>22.416666666666668</v>
       </c>
       <c r="D39" s="21">
         <f>COUNTIFS(tblData[ПричинаПростоя],$B39,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>40</v>
       </c>
       <c r="E39" s="20">
         <f>IF($C$45=0,0,C39/$C$45)</f>
-        <v/>
+        <v>0.05403776617115308</v>
       </c>
       <c r="F39" s="29">
         <f>C39+(10000-ROW())/100000000</f>
-        <v/>
+        <v>22.416766276666667</v>
       </c>
     </row>
     <row r="40">
@@ -3783,19 +3786,19 @@
       </c>
       <c r="C40" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[ПричинаПростоя],$B40,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>10.666666666666666</v>
       </c>
       <c r="D40" s="21">
         <f>COUNTIFS(tblData[ПричинаПростоя],$B40,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="E40" s="20">
         <f>IF($C$45=0,0,C40/$C$45)</f>
-        <v/>
+        <v>0.02571313780634793</v>
       </c>
       <c r="F40" s="29">
         <f>C40+(10000-ROW())/100000000</f>
-        <v/>
+        <v>10.666766266666666</v>
       </c>
     </row>
     <row r="41">
@@ -3806,19 +3809,19 @@
       </c>
       <c r="C41" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[ПричинаПростоя],$B41,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>97.5</v>
       </c>
       <c r="D41" s="21">
         <f>COUNTIFS(tblData[ПричинаПростоя],$B41,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="E41" s="20">
         <f>IF($C$45=0,0,C41/$C$45)</f>
-        <v/>
+        <v>0.23503415026114907</v>
       </c>
       <c r="F41" s="29">
         <f>C41+(10000-ROW())/100000000</f>
-        <v/>
+        <v>97.50009959</v>
       </c>
     </row>
     <row r="42">
@@ -3829,19 +3832,19 @@
       </c>
       <c r="C42" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[ПричинаПростоя],$B42,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>88.66666666666667</v>
       </c>
       <c r="D42" s="21">
         <f>COUNTIFS(tblData[ПричинаПростоя],$B42,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>78</v>
       </c>
       <c r="E42" s="20">
         <f>IF($C$45=0,0,C42/$C$45)</f>
-        <v/>
+        <v>0.2137404580152672</v>
       </c>
       <c r="F42" s="29">
         <f>C42+(10000-ROW())/100000000</f>
-        <v/>
+        <v>88.66676624666667</v>
       </c>
     </row>
     <row r="43">
@@ -3852,19 +3855,19 @@
       </c>
       <c r="C43" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[ПричинаПростоя],$B43,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>46.5</v>
       </c>
       <c r="D43" s="21">
         <f>COUNTIFS(tblData[ПричинаПростоя],$B43,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>21</v>
       </c>
       <c r="E43" s="20">
         <f>IF($C$45=0,0,C43/$C$45)</f>
-        <v/>
+        <v>0.11209321012454801</v>
       </c>
       <c r="F43" s="29">
         <f>C43+(10000-ROW())/100000000</f>
-        <v/>
+        <v>46.50009957</v>
       </c>
     </row>
     <row r="44">
@@ -3875,19 +3878,19 @@
       </c>
       <c r="C44" s="19">
         <f>SUMIFS(tblData[ПростойМин],tblData[ПричинаПростоя],$B44,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>138.41666666666666</v>
       </c>
       <c r="D44" s="21">
         <f>COUNTIFS(tblData[ПричинаПростоя],$B44,tblData[ПростойМин],"&gt;0",tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="E44" s="20">
         <f>IF($C$45=0,0,C44/$C$45)</f>
-        <v/>
+        <v>0.33366813981518684</v>
       </c>
       <c r="F44" s="29">
         <f>C44+(10000-ROW())/100000000</f>
-        <v/>
+        <v>138.41676622666665</v>
       </c>
     </row>
     <row r="45">
@@ -3898,15 +3901,15 @@
       </c>
       <c r="C45" s="23">
         <f>SUM(C38:C44)</f>
-        <v/>
+        <v>414.8333333333333</v>
       </c>
       <c r="D45" s="25">
         <f>SUM(D38:D44)</f>
-        <v/>
+        <v>256</v>
       </c>
       <c r="E45" s="24">
         <f>IF(C45=0,0,1)</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F45" s="27" t="n"/>
     </row>
@@ -3972,35 +3975,35 @@
       </c>
       <c r="C49" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B49,tblData[ПричинаПростоя],C$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>1.6666666666666667</v>
       </c>
       <c r="D49" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B49,tblData[ПричинаПростоя],D$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>5.166666666666667</v>
       </c>
       <c r="E49" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B49,tblData[ПричинаПростоя],E$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F49" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B49,tblData[ПричинаПростоя],F$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>14</v>
       </c>
       <c r="G49" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B49,tblData[ПричинаПростоя],G$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>11.416666666666666</v>
       </c>
       <c r="H49" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B49,tblData[ПричинаПростоя],H$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="I49" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B49,tblData[ПричинаПростоя],I$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>12</v>
       </c>
       <c r="J49" s="31">
         <f>SUM(C49:I49)</f>
-        <v/>
+        <v>44.25</v>
       </c>
     </row>
     <row r="50">
@@ -4011,35 +4014,35 @@
       </c>
       <c r="C50" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B50,tblData[ПричинаПростоя],C$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>0.6666666666666666</v>
       </c>
       <c r="D50" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B50,tblData[ПричинаПростоя],D$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>3.8333333333333335</v>
       </c>
       <c r="E50" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B50,tblData[ПричинаПростоя],E$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F50" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B50,tblData[ПричинаПростоя],F$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>8.333333333333334</v>
       </c>
       <c r="G50" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B50,tblData[ПричинаПростоя],G$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>9.5</v>
       </c>
       <c r="H50" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B50,tblData[ПричинаПростоя],H$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>9.166666666666666</v>
       </c>
       <c r="I50" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B50,tblData[ПричинаПростоя],I$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>8.416666666666666</v>
       </c>
       <c r="J50" s="31">
         <f>SUM(C50:I50)</f>
-        <v/>
+        <v>39.916666666666664</v>
       </c>
     </row>
     <row r="51">
@@ -4050,35 +4053,35 @@
       </c>
       <c r="C51" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B51,tblData[ПричинаПростоя],C$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>2.25</v>
       </c>
       <c r="D51" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B51,tblData[ПричинаПростоя],D$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>2.0833333333333335</v>
       </c>
       <c r="E51" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B51,tblData[ПричинаПростоя],E$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>0.4166666666666667</v>
       </c>
       <c r="F51" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B51,tblData[ПричинаПростоя],F$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>12.583333333333334</v>
       </c>
       <c r="G51" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B51,tblData[ПричинаПростоя],G$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>21.5</v>
       </c>
       <c r="H51" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B51,tblData[ПричинаПростоя],H$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>13.583333333333334</v>
       </c>
       <c r="I51" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B51,tblData[ПричинаПростоя],I$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>20.166666666666668</v>
       </c>
       <c r="J51" s="31">
         <f>SUM(C51:I51)</f>
-        <v/>
+        <v>72.58333333333334</v>
       </c>
     </row>
     <row r="52">
@@ -4089,35 +4092,35 @@
       </c>
       <c r="C52" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B52,tblData[ПричинаПростоя],C$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>2.3333333333333335</v>
       </c>
       <c r="D52" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B52,tblData[ПричинаПростоя],D$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>2.3333333333333335</v>
       </c>
       <c r="E52" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B52,tblData[ПричинаПростоя],E$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>5.666666666666667</v>
       </c>
       <c r="F52" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B52,tblData[ПричинаПростоя],F$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>22.25</v>
       </c>
       <c r="G52" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B52,tblData[ПричинаПростоя],G$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>13.333333333333334</v>
       </c>
       <c r="H52" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B52,tblData[ПричинаПростоя],H$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>3.8333333333333335</v>
       </c>
       <c r="I52" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B52,tblData[ПричинаПростоя],I$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>41.833333333333336</v>
       </c>
       <c r="J52" s="31">
         <f>SUM(C52:I52)</f>
-        <v/>
+        <v>91.58333333333334</v>
       </c>
     </row>
     <row r="53">
@@ -4128,35 +4131,35 @@
       </c>
       <c r="C53" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B53,tblData[ПричинаПростоя],C$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>0.5</v>
       </c>
       <c r="D53" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B53,tblData[ПричинаПростоя],D$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>2.8333333333333335</v>
       </c>
       <c r="E53" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B53,tblData[ПричинаПростоя],E$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>1.0833333333333333</v>
       </c>
       <c r="F53" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B53,tblData[ПричинаПростоя],F$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>15.666666666666666</v>
       </c>
       <c r="G53" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B53,tblData[ПричинаПростоя],G$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>8.5</v>
       </c>
       <c r="H53" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B53,tblData[ПричинаПростоя],H$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>7</v>
       </c>
       <c r="I53" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B53,tblData[ПричинаПростоя],I$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>18.416666666666668</v>
       </c>
       <c r="J53" s="31">
         <f>SUM(C53:I53)</f>
-        <v/>
+        <v>54</v>
       </c>
     </row>
     <row r="54">
@@ -4167,35 +4170,35 @@
       </c>
       <c r="C54" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B54,tblData[ПричинаПростоя],C$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>0.75</v>
       </c>
       <c r="D54" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B54,tblData[ПричинаПростоя],D$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="E54" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B54,tblData[ПричинаПростоя],E$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="F54" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B54,tblData[ПричинаПростоя],F$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>2.8333333333333335</v>
       </c>
       <c r="G54" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B54,tblData[ПричинаПростоя],G$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>4.75</v>
       </c>
       <c r="H54" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B54,tblData[ПричинаПростоя],H$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>4.5</v>
       </c>
       <c r="I54" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B54,tblData[ПричинаПростоя],I$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>3.1666666666666665</v>
       </c>
       <c r="J54" s="31">
         <f>SUM(C54:I54)</f>
-        <v/>
+        <v>18</v>
       </c>
     </row>
     <row r="55">
@@ -4206,35 +4209,35 @@
       </c>
       <c r="C55" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B55,tblData[ПричинаПростоя],C$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>1.4166666666666667</v>
       </c>
       <c r="D55" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B55,tblData[ПричинаПростоя],D$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>1.3333333333333333</v>
       </c>
       <c r="E55" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B55,tblData[ПричинаПростоя],E$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>2.5</v>
       </c>
       <c r="F55" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B55,tblData[ПричинаПростоя],F$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>12.416666666666666</v>
       </c>
       <c r="G55" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B55,tblData[ПричинаПростоя],G$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>11.75</v>
       </c>
       <c r="H55" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B55,tblData[ПричинаПростоя],H$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>1.5833333333333333</v>
       </c>
       <c r="I55" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B55,tblData[ПричинаПростоя],I$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>13.916666666666666</v>
       </c>
       <c r="J55" s="31">
         <f>SUM(C55:I55)</f>
-        <v/>
+        <v>44.916666666666664</v>
       </c>
     </row>
     <row r="56">
@@ -4245,35 +4248,35 @@
       </c>
       <c r="C56" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B56,tblData[ПричинаПростоя],C$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>1.0833333333333333</v>
       </c>
       <c r="D56" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B56,tblData[ПричинаПростоя],D$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>2.8333333333333335</v>
       </c>
       <c r="E56" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B56,tblData[ПричинаПростоя],E$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="F56" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B56,tblData[ПричинаПростоя],F$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>9.416666666666666</v>
       </c>
       <c r="G56" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B56,tblData[ПричинаПростоя],G$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>7.916666666666667</v>
       </c>
       <c r="H56" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B56,tblData[ПричинаПростоя],H$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>6.833333333333333</v>
       </c>
       <c r="I56" s="30">
         <f>SUMIFS(tblData[ПростойМин],tblData[Оборудование],$B56,tblData[ПричинаПростоя],I$48,tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)/60</f>
-        <v/>
+        <v>20.5</v>
       </c>
       <c r="J56" s="31">
         <f>SUM(C56:I56)</f>
-        <v/>
+        <v>49.583333333333336</v>
       </c>
     </row>
     <row r="57">
@@ -4284,35 +4287,35 @@
       </c>
       <c r="C57" s="32">
         <f>SUM(C49:C56)</f>
-        <v/>
+        <v>10.666666666666666</v>
       </c>
       <c r="D57" s="32">
         <f>SUM(D49:D56)</f>
-        <v/>
+        <v>22.416666666666668</v>
       </c>
       <c r="E57" s="32">
         <f>SUM(E49:E56)</f>
-        <v/>
+        <v>10.666666666666666</v>
       </c>
       <c r="F57" s="32">
         <f>SUM(F49:F56)</f>
-        <v/>
+        <v>97.5</v>
       </c>
       <c r="G57" s="32">
         <f>SUM(G49:G56)</f>
-        <v/>
+        <v>88.66666666666667</v>
       </c>
       <c r="H57" s="32">
         <f>SUM(H49:H56)</f>
-        <v/>
+        <v>46.5</v>
       </c>
       <c r="I57" s="32">
         <f>SUM(I49:I56)</f>
-        <v/>
+        <v>138.41666666666666</v>
       </c>
       <c r="J57" s="32">
         <f>SUM(J49:J56)</f>
-        <v/>
+        <v>414.83333333333337</v>
       </c>
     </row>
   </sheetData>
@@ -4460,9 +4463,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="37">
+      <c r="B11" s="37" t="str">
         <f>IF(AND(ISNUMBER(selFrom),ISNUMBER(selTo),selTo&lt;selFrom),"⚠ «Дата по» раньше, чем «Дата с» — все итоги будут равны 0","✓ Фильтры заданы корректно")</f>
-        <v/>
+        <v>✓ Фильтры заданы корректно</v>
       </c>
     </row>
     <row r="13">
@@ -4480,7 +4483,7 @@
       </c>
       <c r="C14" s="38">
         <f>COUNT(tblData[Дата])</f>
-        <v/>
+        <v>412</v>
       </c>
     </row>
     <row r="15">
@@ -4491,7 +4494,7 @@
       </c>
       <c r="C15" s="39">
         <f>MIN(tblData[Дата])</f>
-        <v/>
+        <v>46266</v>
       </c>
     </row>
     <row r="16">
@@ -4502,7 +4505,7 @@
       </c>
       <c r="C16" s="39">
         <f>MAX(tblData[Дата])</f>
-        <v/>
+        <v>46295</v>
       </c>
     </row>
     <row r="17">
@@ -4513,7 +4516,7 @@
       </c>
       <c r="C17" s="38">
         <f>COUNTIFS(tblData[Смена],critShift,tblData[Цех],critDept,tblData[Дата],"&gt;="&amp;dFrom,tblData[Дата],"&lt;="&amp;dTo)</f>
-        <v/>
+        <v>412</v>
       </c>
     </row>
     <row r="19">
@@ -18878,7 +18881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D31"/>
+  <dimension ref="B1:D37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -18909,126 +18912,96 @@
           <t>Итог</t>
         </is>
       </c>
-      <c r="C4" s="47" t="inlineStr">
-        <is>
-          <t>412 of 417 rows accepted; dropped_duplicate: 3; filled_blank_reason: 5; normalised_machine: 6; normalised_shift: 9; rejected_bad_date: 1; rejected_negative: 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="16" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Принято строк: 412 из 417</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="48" t="inlineStr">
+        <is>
+          <t>Отклонено: дата не распознана</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="48" t="inlineStr">
+        <is>
+          <t>Отклонено: отрицательное значение</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="26" t="inlineStr">
+        <is>
+          <t>Удалено: дубликат строки</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Заполнено: простой без причины</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="47" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>Приведено написание (оборудование)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="47" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>Приведено написание (смена)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Строка CSV</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Действие</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
         <is>
           <t>Подробности</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="28" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="26" t="inlineStr">
-        <is>
-          <t>Приведено написание (shift)</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="inlineStr">
-        <is>
-          <t>'дневная' -&gt; 'Дневная'</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="28" t="n">
-        <v>30</v>
-      </c>
-      <c r="C8" s="26" t="inlineStr">
-        <is>
-          <t>Приведено написание (shift)</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="inlineStr">
-        <is>
-          <t>'дневная' -&gt; 'Дневная'</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="28" t="n">
-        <v>31</v>
-      </c>
-      <c r="C9" s="26" t="inlineStr">
-        <is>
-          <t>Приведено написание (machine)</t>
-        </is>
-      </c>
-      <c r="D9" s="26" t="inlineStr">
-        <is>
-          <t>'asm-01' -&gt; 'ASM-01'</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="28" t="n">
-        <v>53</v>
-      </c>
-      <c r="C10" s="26" t="inlineStr">
-        <is>
-          <t>Приведено написание (machine)</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="inlineStr">
-        <is>
-          <t>'wld-01' -&gt; 'WLD-01'</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="28" t="n">
-        <v>60</v>
-      </c>
-      <c r="C11" s="26" t="inlineStr">
-        <is>
-          <t>Заполнено: простой без причины</t>
-        </is>
-      </c>
-      <c r="D11" s="26" t="inlineStr">
-        <is>
-          <t>Не указана</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="28" t="n">
-        <v>65</v>
-      </c>
-      <c r="C12" s="26" t="inlineStr">
-        <is>
-          <t>Приведено написание (shift)</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="inlineStr">
-        <is>
-          <t>'дневная' -&gt; 'Дневная'</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="28" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>Приведено написание (shift)</t>
+          <t>Приведено написание (смена)</t>
         </is>
       </c>
       <c r="D13" s="26" t="inlineStr">
@@ -19039,86 +19012,86 @@
     </row>
     <row r="14">
       <c r="B14" s="28" t="n">
-        <v>89</v>
+        <v>30</v>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>Удалено: дубликат строки</t>
+          <t>Приведено написание (смена)</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">
         <is>
-          <t>exact duplicate of an earlier row</t>
+          <t>'дневная' -&gt; 'Дневная'</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="28" t="n">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="C15" s="26" t="inlineStr">
         <is>
-          <t>Приведено написание (machine)</t>
+          <t>Приведено написание (оборудование)</t>
         </is>
       </c>
       <c r="D15" s="26" t="inlineStr">
         <is>
-          <t>'cnc-02' -&gt; 'CNC-02'</t>
+          <t>'asm-01' -&gt; 'ASM-01'</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="28" t="n">
-        <v>130</v>
+        <v>53</v>
       </c>
       <c r="C16" s="26" t="inlineStr">
         <is>
-          <t>Заполнено: простой без причины</t>
+          <t>Приведено написание (оборудование)</t>
         </is>
       </c>
       <c r="D16" s="26" t="inlineStr">
         <is>
-          <t>Не указана</t>
+          <t>'wld-01' -&gt; 'WLD-01'</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="28" t="n">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="C17" s="26" t="inlineStr">
         <is>
-          <t>Приведено написание (shift)</t>
+          <t>Заполнено: простой без причины</t>
         </is>
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
-          <t>'дневная' -&gt; 'Дневная'</t>
+          <t>Не указана</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="28" t="n">
-        <v>198</v>
+        <v>65</v>
       </c>
       <c r="C18" s="26" t="inlineStr">
         <is>
-          <t>Удалено: дубликат строки</t>
+          <t>Приведено написание (смена)</t>
         </is>
       </c>
       <c r="D18" s="26" t="inlineStr">
         <is>
-          <t>exact duplicate of an earlier row</t>
+          <t>'дневная' -&gt; 'Дневная'</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="28" t="n">
-        <v>211</v>
+        <v>77</v>
       </c>
       <c r="C19" s="26" t="inlineStr">
         <is>
-          <t>Приведено написание (shift)</t>
+          <t>Приведено написание (смена)</t>
         </is>
       </c>
       <c r="D19" s="26" t="inlineStr">
@@ -19129,185 +19102,276 @@
     </row>
     <row r="20">
       <c r="B20" s="28" t="n">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C20" s="26" t="inlineStr">
         <is>
-          <t>Приведено написание (shift)</t>
+          <t>Удалено: дубликат строки</t>
         </is>
       </c>
       <c r="D20" s="26" t="inlineStr">
         <is>
-          <t>'дневная' -&gt; 'Дневная'</t>
+          <t>точный дубликат одной из строк выше</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="28" t="n">
-        <v>261</v>
+        <v>120</v>
       </c>
       <c r="C21" s="26" t="inlineStr">
         <is>
-          <t>Удалено: дубликат строки</t>
+          <t>Приведено написание (оборудование)</t>
         </is>
       </c>
       <c r="D21" s="26" t="inlineStr">
         <is>
-          <t>exact duplicate of an earlier row</t>
+          <t>'cnc-02' -&gt; 'CNC-02'</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="28" t="n">
-        <v>266</v>
+        <v>130</v>
       </c>
       <c r="C22" s="26" t="inlineStr">
         <is>
-          <t>Приведено написание (machine)</t>
+          <t>Заполнено: простой без причины</t>
         </is>
       </c>
       <c r="D22" s="26" t="inlineStr">
         <is>
-          <t>'cnc-02' -&gt; 'CNC-02'</t>
+          <t>Не указана</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="28" t="n">
-        <v>274</v>
+        <v>147</v>
       </c>
       <c r="C23" s="26" t="inlineStr">
         <is>
-          <t>Приведено написание (shift)</t>
+          <t>Приведено написание (смена)</t>
         </is>
       </c>
       <c r="D23" s="26" t="inlineStr">
         <is>
-          <t>'вечерняя' -&gt; 'Вечерняя'</t>
+          <t>'дневная' -&gt; 'Дневная'</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="28" t="n">
-        <v>275</v>
+        <v>198</v>
       </c>
       <c r="C24" s="26" t="inlineStr">
         <is>
-          <t>Заполнено: простой без причины</t>
+          <t>Удалено: дубликат строки</t>
         </is>
       </c>
       <c r="D24" s="26" t="inlineStr">
         <is>
-          <t>Не указана</t>
+          <t>точный дубликат одной из строк выше</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="28" t="n">
-        <v>302</v>
+        <v>211</v>
       </c>
       <c r="C25" s="26" t="inlineStr">
         <is>
-          <t>Приведено написание (shift)</t>
+          <t>Приведено написание (смена)</t>
         </is>
       </c>
       <c r="D25" s="26" t="inlineStr">
         <is>
-          <t>'вечерняя' -&gt; 'Вечерняя'</t>
+          <t>'дневная' -&gt; 'Дневная'</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="28" t="n">
-        <v>341</v>
+        <v>258</v>
       </c>
       <c r="C26" s="26" t="inlineStr">
         <is>
-          <t>Приведено написание (machine)</t>
+          <t>Приведено написание (смена)</t>
         </is>
       </c>
       <c r="D26" s="26" t="inlineStr">
         <is>
-          <t>'cnc-01' -&gt; 'CNC-01'</t>
+          <t>'дневная' -&gt; 'Дневная'</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="28" t="n">
-        <v>348</v>
+        <v>261</v>
       </c>
       <c r="C27" s="26" t="inlineStr">
         <is>
-          <t>Заполнено: простой без причины</t>
+          <t>Удалено: дубликат строки</t>
         </is>
       </c>
       <c r="D27" s="26" t="inlineStr">
         <is>
-          <t>Не указана</t>
+          <t>точный дубликат одной из строк выше</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="28" t="n">
-        <v>356</v>
+        <v>266</v>
       </c>
       <c r="C28" s="26" t="inlineStr">
         <is>
-          <t>Заполнено: простой без причины</t>
+          <t>Приведено написание (оборудование)</t>
         </is>
       </c>
       <c r="D28" s="26" t="inlineStr">
         <is>
-          <t>Не указана</t>
+          <t>'cnc-02' -&gt; 'CNC-02'</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="28" t="n">
-        <v>360</v>
-      </c>
-      <c r="C29" s="48" t="inlineStr">
-        <is>
-          <t>Отклонено: отрицательное значение</t>
+        <v>274</v>
+      </c>
+      <c r="C29" s="26" t="inlineStr">
+        <is>
+          <t>Приведено написание (смена)</t>
         </is>
       </c>
       <c r="D29" s="26" t="inlineStr">
         <is>
-          <t>run=8.0, halt=-15.0</t>
+          <t>'вечерняя' -&gt; 'Вечерняя'</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="28" t="n">
-        <v>369</v>
-      </c>
-      <c r="C30" s="48" t="inlineStr">
-        <is>
-          <t>Отклонено: дата не распознана</t>
+        <v>275</v>
+      </c>
+      <c r="C30" s="26" t="inlineStr">
+        <is>
+          <t>Заполнено: простой без причины</t>
         </is>
       </c>
       <c r="D30" s="26" t="inlineStr">
         <is>
-          <t>unrecognised date '45.13.2026'</t>
+          <t>Не указана</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="28" t="n">
+        <v>302</v>
+      </c>
+      <c r="C31" s="26" t="inlineStr">
+        <is>
+          <t>Приведено написание (смена)</t>
+        </is>
+      </c>
+      <c r="D31" s="26" t="inlineStr">
+        <is>
+          <t>'вечерняя' -&gt; 'Вечерняя'</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="28" t="n">
+        <v>341</v>
+      </c>
+      <c r="C32" s="26" t="inlineStr">
+        <is>
+          <t>Приведено написание (оборудование)</t>
+        </is>
+      </c>
+      <c r="D32" s="26" t="inlineStr">
+        <is>
+          <t>'cnc-01' -&gt; 'CNC-01'</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="28" t="n">
+        <v>348</v>
+      </c>
+      <c r="C33" s="26" t="inlineStr">
+        <is>
+          <t>Заполнено: простой без причины</t>
+        </is>
+      </c>
+      <c r="D33" s="26" t="inlineStr">
+        <is>
+          <t>Не указана</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="28" t="n">
+        <v>356</v>
+      </c>
+      <c r="C34" s="26" t="inlineStr">
+        <is>
+          <t>Заполнено: простой без причины</t>
+        </is>
+      </c>
+      <c r="D34" s="26" t="inlineStr">
+        <is>
+          <t>Не указана</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="28" t="n">
+        <v>360</v>
+      </c>
+      <c r="C35" s="48" t="inlineStr">
+        <is>
+          <t>Отклонено: отрицательное значение</t>
+        </is>
+      </c>
+      <c r="D35" s="26" t="inlineStr">
+        <is>
+          <t>работа=8.0, простой=-15.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="28" t="n">
+        <v>369</v>
+      </c>
+      <c r="C36" s="48" t="inlineStr">
+        <is>
+          <t>Отклонено: дата не распознана</t>
+        </is>
+      </c>
+      <c r="D36" s="26" t="inlineStr">
+        <is>
+          <t>не удалось распознать дату '45.13.2026'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="28" t="n">
         <v>407</v>
       </c>
-      <c r="C31" s="26" t="inlineStr">
-        <is>
-          <t>Приведено написание (machine)</t>
-        </is>
-      </c>
-      <c r="D31" s="26" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
+        <is>
+          <t>Приведено написание (оборудование)</t>
+        </is>
+      </c>
+      <c r="D37" s="26" t="inlineStr">
         <is>
           <t>'cnc-02' -&gt; 'CNC-02'</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B12:D37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19363,20 +19427,20 @@
       </c>
       <c r="C2" s="49">
         <f>MIN(tblData[Дата])</f>
-        <v/>
+        <v>46266</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
           <t>Shift criterion</t>
         </is>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
         <f>IF(OR(selShift="",selShift=$A$2),"*",selShift)</f>
-        <v/>
+        <v>*</v>
       </c>
       <c r="H2" s="50">
         <f>tgtAvail</f>
-        <v/>
+        <v>0.85</v>
       </c>
     </row>
     <row r="3">
@@ -19392,20 +19456,20 @@
       </c>
       <c r="C3" s="49">
         <f>IF(C2="","",IF(C2+1&gt;MAX(tblData[Дата]),"",C2+1))</f>
-        <v/>
+        <v>46267</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
           <t>Department criterion</t>
         </is>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
         <f>IF(OR(selDept="",selDept=$B$2),"*",selDept)</f>
-        <v/>
+        <v>*</v>
       </c>
       <c r="H3" s="50">
         <f>tgtAvail</f>
-        <v/>
+        <v>0.85</v>
       </c>
     </row>
     <row r="4">
@@ -19421,7 +19485,7 @@
       </c>
       <c r="C4" s="49">
         <f>IF(C3="","",IF(C3+1&gt;MAX(tblData[Дата]),"",C3+1))</f>
-        <v/>
+        <v>46268</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -19430,11 +19494,11 @@
       </c>
       <c r="F4" s="49">
         <f>IF(ISNUMBER(selFrom),selFrom,MIN(tblData[Дата]))</f>
-        <v/>
+        <v>46266</v>
       </c>
       <c r="H4" s="50">
         <f>tgtAvail</f>
-        <v/>
+        <v>0.85</v>
       </c>
     </row>
     <row r="5">
@@ -19450,7 +19514,7 @@
       </c>
       <c r="C5" s="49">
         <f>IF(C4="","",IF(C4+1&gt;MAX(tblData[Дата]),"",C4+1))</f>
-        <v/>
+        <v>46269</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -19459,11 +19523,11 @@
       </c>
       <c r="F5" s="49">
         <f>IF(ISNUMBER(selTo),selTo,MAX(tblData[Дата]))</f>
-        <v/>
+        <v>46295</v>
       </c>
       <c r="H5" s="50">
         <f>tgtAvail</f>
-        <v/>
+        <v>0.85</v>
       </c>
     </row>
     <row r="6">
@@ -19474,49 +19538,49 @@
       </c>
       <c r="C6" s="49">
         <f>IF(C5="","",IF(C5+1&gt;MAX(tblData[Дата]),"",C5+1))</f>
-        <v/>
+        <v>46270</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
           <t>Period text</t>
         </is>
       </c>
-      <c r="F6">
+      <c r="F6" t="str">
         <f>RIGHT("0"&amp;DAY(dFrom),2)&amp;"."&amp;RIGHT("0"&amp;MONTH(dFrom),2)&amp;"."&amp;YEAR(dFrom)&amp;" – "&amp;RIGHT("0"&amp;DAY(dTo),2)&amp;"."&amp;RIGHT("0"&amp;MONTH(dTo),2)&amp;"."&amp;YEAR(dTo)</f>
-        <v/>
+        <v>01.09.2026 – 30.09.2026</v>
       </c>
     </row>
     <row r="7">
       <c r="C7" s="49">
         <f>IF(C6="","",IF(C6+1&gt;MAX(tblData[Дата]),"",C6+1))</f>
-        <v/>
+        <v>46271</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>Caption</t>
         </is>
       </c>
-      <c r="F7">
+      <c r="F7" t="str">
         <f>"Смена: "&amp;IF(critShift="*",$A$2,selShift)&amp;"   ·   Цех: "&amp;IF(critDept="*",$B$2,selDept)&amp;"   ·   Период: "&amp;periodText</f>
-        <v/>
+        <v>Смена: Все   ·   Цех: Все   ·   Период: 01.09.2026 – 30.09.2026</v>
       </c>
     </row>
     <row r="8">
       <c r="C8" s="49">
         <f>IF(C7="","",IF(C7+1&gt;MAX(tblData[Дата]),"",C7+1))</f>
-        <v/>
+        <v>46272</v>
       </c>
     </row>
     <row r="9">
       <c r="C9" s="49">
         <f>IF(C8="","",IF(C8+1&gt;MAX(tblData[Дата]),"",C8+1))</f>
-        <v/>
+        <v>46273</v>
       </c>
     </row>
     <row r="10">
       <c r="C10" s="49">
         <f>IF(C9="","",IF(C9+1&gt;MAX(tblData[Дата]),"",C9+1))</f>
-        <v/>
+        <v>46274</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -19527,2345 +19591,2345 @@
     <row r="11">
       <c r="C11" s="49">
         <f>IF(C10="","",IF(C10+1&gt;MAX(tblData[Дата]),"",C10+1))</f>
-        <v/>
+        <v>46275</v>
       </c>
     </row>
     <row r="12">
       <c r="C12" s="49">
         <f>IF(C11="","",IF(C11+1&gt;MAX(tblData[Дата]),"",C11+1))</f>
-        <v/>
+        <v>46276</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="49">
         <f>IF(C12="","",IF(C12+1&gt;MAX(tblData[Дата]),"",C12+1))</f>
-        <v/>
+        <v>46277</v>
       </c>
     </row>
     <row r="14">
       <c r="C14" s="49">
         <f>IF(C13="","",IF(C13+1&gt;MAX(tblData[Дата]),"",C13+1))</f>
-        <v/>
+        <v>46278</v>
       </c>
     </row>
     <row r="15">
       <c r="C15" s="49">
         <f>IF(C14="","",IF(C14+1&gt;MAX(tblData[Дата]),"",C14+1))</f>
-        <v/>
+        <v>46279</v>
       </c>
     </row>
     <row r="16">
       <c r="C16" s="49">
         <f>IF(C15="","",IF(C15+1&gt;MAX(tblData[Дата]),"",C15+1))</f>
-        <v/>
+        <v>46280</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="49">
         <f>IF(C16="","",IF(C16+1&gt;MAX(tblData[Дата]),"",C16+1))</f>
-        <v/>
+        <v>46281</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="49">
         <f>IF(C17="","",IF(C17+1&gt;MAX(tblData[Дата]),"",C17+1))</f>
-        <v/>
+        <v>46282</v>
       </c>
     </row>
     <row r="19">
       <c r="C19" s="49">
         <f>IF(C18="","",IF(C18+1&gt;MAX(tblData[Дата]),"",C18+1))</f>
-        <v/>
+        <v>46283</v>
       </c>
     </row>
     <row r="20">
       <c r="C20" s="49">
         <f>IF(C19="","",IF(C19+1&gt;MAX(tblData[Дата]),"",C19+1))</f>
-        <v/>
+        <v>46284</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" s="49">
         <f>IF(C20="","",IF(C20+1&gt;MAX(tblData[Дата]),"",C20+1))</f>
-        <v/>
+        <v>46285</v>
       </c>
     </row>
     <row r="22">
       <c r="C22" s="49">
         <f>IF(C21="","",IF(C21+1&gt;MAX(tblData[Дата]),"",C21+1))</f>
-        <v/>
+        <v>46286</v>
       </c>
     </row>
     <row r="23">
       <c r="C23" s="49">
         <f>IF(C22="","",IF(C22+1&gt;MAX(tblData[Дата]),"",C22+1))</f>
-        <v/>
+        <v>46287</v>
       </c>
     </row>
     <row r="24">
       <c r="C24" s="49">
         <f>IF(C23="","",IF(C23+1&gt;MAX(tblData[Дата]),"",C23+1))</f>
-        <v/>
+        <v>46288</v>
       </c>
     </row>
     <row r="25">
       <c r="C25" s="49">
         <f>IF(C24="","",IF(C24+1&gt;MAX(tblData[Дата]),"",C24+1))</f>
-        <v/>
+        <v>46289</v>
       </c>
     </row>
     <row r="26">
       <c r="C26" s="49">
         <f>IF(C25="","",IF(C25+1&gt;MAX(tblData[Дата]),"",C25+1))</f>
-        <v/>
+        <v>46290</v>
       </c>
     </row>
     <row r="27">
       <c r="C27" s="49">
         <f>IF(C26="","",IF(C26+1&gt;MAX(tblData[Дата]),"",C26+1))</f>
-        <v/>
+        <v>46291</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" s="49">
         <f>IF(C27="","",IF(C27+1&gt;MAX(tblData[Дата]),"",C27+1))</f>
-        <v/>
+        <v>46292</v>
       </c>
     </row>
     <row r="29">
       <c r="C29" s="49">
         <f>IF(C28="","",IF(C28+1&gt;MAX(tblData[Дата]),"",C28+1))</f>
-        <v/>
+        <v>46293</v>
       </c>
     </row>
     <row r="30">
       <c r="C30" s="49">
         <f>IF(C29="","",IF(C29+1&gt;MAX(tblData[Дата]),"",C29+1))</f>
-        <v/>
+        <v>46294</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" s="49">
         <f>IF(C30="","",IF(C30+1&gt;MAX(tblData[Дата]),"",C30+1))</f>
-        <v/>
+        <v>46295</v>
       </c>
     </row>
     <row r="32">
-      <c r="C32" s="49">
+      <c r="C32" s="49" t="str">
         <f>IF(C31="","",IF(C31+1&gt;MAX(tblData[Дата]),"",C31+1))</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="C33" s="49">
+      <c r="C33" s="49" t="str">
         <f>IF(C32="","",IF(C32+1&gt;MAX(tblData[Дата]),"",C32+1))</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="C34" s="49">
+      <c r="C34" s="49" t="str">
         <f>IF(C33="","",IF(C33+1&gt;MAX(tblData[Дата]),"",C33+1))</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="C35" s="49">
+      <c r="C35" s="49" t="str">
         <f>IF(C34="","",IF(C34+1&gt;MAX(tblData[Дата]),"",C34+1))</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="C36" s="49">
+      <c r="C36" s="49" t="str">
         <f>IF(C35="","",IF(C35+1&gt;MAX(tblData[Дата]),"",C35+1))</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="C37" s="49">
+      <c r="C37" s="49" t="str">
         <f>IF(C36="","",IF(C36+1&gt;MAX(tblData[Дата]),"",C36+1))</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="C38" s="49">
+      <c r="C38" s="49" t="str">
         <f>IF(C37="","",IF(C37+1&gt;MAX(tblData[Дата]),"",C37+1))</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="C39" s="49">
+      <c r="C39" s="49" t="str">
         <f>IF(C38="","",IF(C38+1&gt;MAX(tblData[Дата]),"",C38+1))</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="C40" s="49">
+      <c r="C40" s="49" t="str">
         <f>IF(C39="","",IF(C39+1&gt;MAX(tblData[Дата]),"",C39+1))</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="C41" s="49">
+      <c r="C41" s="49" t="str">
         <f>IF(C40="","",IF(C40+1&gt;MAX(tblData[Дата]),"",C40+1))</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="C42" s="49">
+      <c r="C42" s="49" t="str">
         <f>IF(C41="","",IF(C41+1&gt;MAX(tblData[Дата]),"",C41+1))</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="C43" s="49">
+      <c r="C43" s="49" t="str">
         <f>IF(C42="","",IF(C42+1&gt;MAX(tblData[Дата]),"",C42+1))</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="C44" s="49">
+      <c r="C44" s="49" t="str">
         <f>IF(C43="","",IF(C43+1&gt;MAX(tblData[Дата]),"",C43+1))</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="49">
+      <c r="C45" s="49" t="str">
         <f>IF(C44="","",IF(C44+1&gt;MAX(tblData[Дата]),"",C44+1))</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="C46" s="49">
+      <c r="C46" s="49" t="str">
         <f>IF(C45="","",IF(C45+1&gt;MAX(tblData[Дата]),"",C45+1))</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="C47" s="49">
+      <c r="C47" s="49" t="str">
         <f>IF(C46="","",IF(C46+1&gt;MAX(tblData[Дата]),"",C46+1))</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="C48" s="49">
+      <c r="C48" s="49" t="str">
         <f>IF(C47="","",IF(C47+1&gt;MAX(tblData[Дата]),"",C47+1))</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="C49" s="49">
+      <c r="C49" s="49" t="str">
         <f>IF(C48="","",IF(C48+1&gt;MAX(tblData[Дата]),"",C48+1))</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="C50" s="49">
+      <c r="C50" s="49" t="str">
         <f>IF(C49="","",IF(C49+1&gt;MAX(tblData[Дата]),"",C49+1))</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="C51" s="49">
+      <c r="C51" s="49" t="str">
         <f>IF(C50="","",IF(C50+1&gt;MAX(tblData[Дата]),"",C50+1))</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="C52" s="49">
+      <c r="C52" s="49" t="str">
         <f>IF(C51="","",IF(C51+1&gt;MAX(tblData[Дата]),"",C51+1))</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="C53" s="49">
+      <c r="C53" s="49" t="str">
         <f>IF(C52="","",IF(C52+1&gt;MAX(tblData[Дата]),"",C52+1))</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="C54" s="49">
+      <c r="C54" s="49" t="str">
         <f>IF(C53="","",IF(C53+1&gt;MAX(tblData[Дата]),"",C53+1))</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="C55" s="49">
+      <c r="C55" s="49" t="str">
         <f>IF(C54="","",IF(C54+1&gt;MAX(tblData[Дата]),"",C54+1))</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="C56" s="49">
+      <c r="C56" s="49" t="str">
         <f>IF(C55="","",IF(C55+1&gt;MAX(tblData[Дата]),"",C55+1))</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="C57" s="49">
+      <c r="C57" s="49" t="str">
         <f>IF(C56="","",IF(C56+1&gt;MAX(tblData[Дата]),"",C56+1))</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="C58" s="49">
+      <c r="C58" s="49" t="str">
         <f>IF(C57="","",IF(C57+1&gt;MAX(tblData[Дата]),"",C57+1))</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="C59" s="49">
+      <c r="C59" s="49" t="str">
         <f>IF(C58="","",IF(C58+1&gt;MAX(tblData[Дата]),"",C58+1))</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="C60" s="49">
+      <c r="C60" s="49" t="str">
         <f>IF(C59="","",IF(C59+1&gt;MAX(tblData[Дата]),"",C59+1))</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="C61" s="49">
+      <c r="C61" s="49" t="str">
         <f>IF(C60="","",IF(C60+1&gt;MAX(tblData[Дата]),"",C60+1))</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="C62" s="49">
+      <c r="C62" s="49" t="str">
         <f>IF(C61="","",IF(C61+1&gt;MAX(tblData[Дата]),"",C61+1))</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="C63" s="49">
+      <c r="C63" s="49" t="str">
         <f>IF(C62="","",IF(C62+1&gt;MAX(tblData[Дата]),"",C62+1))</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="C64" s="49">
+      <c r="C64" s="49" t="str">
         <f>IF(C63="","",IF(C63+1&gt;MAX(tblData[Дата]),"",C63+1))</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="C65" s="49">
+      <c r="C65" s="49" t="str">
         <f>IF(C64="","",IF(C64+1&gt;MAX(tblData[Дата]),"",C64+1))</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="C66" s="49">
+      <c r="C66" s="49" t="str">
         <f>IF(C65="","",IF(C65+1&gt;MAX(tblData[Дата]),"",C65+1))</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="C67" s="49">
+      <c r="C67" s="49" t="str">
         <f>IF(C66="","",IF(C66+1&gt;MAX(tblData[Дата]),"",C66+1))</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="C68" s="49">
+      <c r="C68" s="49" t="str">
         <f>IF(C67="","",IF(C67+1&gt;MAX(tblData[Дата]),"",C67+1))</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="C69" s="49">
+      <c r="C69" s="49" t="str">
         <f>IF(C68="","",IF(C68+1&gt;MAX(tblData[Дата]),"",C68+1))</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="C70" s="49">
+      <c r="C70" s="49" t="str">
         <f>IF(C69="","",IF(C69+1&gt;MAX(tblData[Дата]),"",C69+1))</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="C71" s="49">
+      <c r="C71" s="49" t="str">
         <f>IF(C70="","",IF(C70+1&gt;MAX(tblData[Дата]),"",C70+1))</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="C72" s="49">
+      <c r="C72" s="49" t="str">
         <f>IF(C71="","",IF(C71+1&gt;MAX(tblData[Дата]),"",C71+1))</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="C73" s="49">
+      <c r="C73" s="49" t="str">
         <f>IF(C72="","",IF(C72+1&gt;MAX(tblData[Дата]),"",C72+1))</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="C74" s="49">
+      <c r="C74" s="49" t="str">
         <f>IF(C73="","",IF(C73+1&gt;MAX(tblData[Дата]),"",C73+1))</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="C75" s="49">
+      <c r="C75" s="49" t="str">
         <f>IF(C74="","",IF(C74+1&gt;MAX(tblData[Дата]),"",C74+1))</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="C76" s="49">
+      <c r="C76" s="49" t="str">
         <f>IF(C75="","",IF(C75+1&gt;MAX(tblData[Дата]),"",C75+1))</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="C77" s="49">
+      <c r="C77" s="49" t="str">
         <f>IF(C76="","",IF(C76+1&gt;MAX(tblData[Дата]),"",C76+1))</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="C78" s="49">
+      <c r="C78" s="49" t="str">
         <f>IF(C77="","",IF(C77+1&gt;MAX(tblData[Дата]),"",C77+1))</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="C79" s="49">
+      <c r="C79" s="49" t="str">
         <f>IF(C78="","",IF(C78+1&gt;MAX(tblData[Дата]),"",C78+1))</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="C80" s="49">
+      <c r="C80" s="49" t="str">
         <f>IF(C79="","",IF(C79+1&gt;MAX(tblData[Дата]),"",C79+1))</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="C81" s="49">
+      <c r="C81" s="49" t="str">
         <f>IF(C80="","",IF(C80+1&gt;MAX(tblData[Дата]),"",C80+1))</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="C82" s="49">
+      <c r="C82" s="49" t="str">
         <f>IF(C81="","",IF(C81+1&gt;MAX(tblData[Дата]),"",C81+1))</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="C83" s="49">
+      <c r="C83" s="49" t="str">
         <f>IF(C82="","",IF(C82+1&gt;MAX(tblData[Дата]),"",C82+1))</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="C84" s="49">
+      <c r="C84" s="49" t="str">
         <f>IF(C83="","",IF(C83+1&gt;MAX(tblData[Дата]),"",C83+1))</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="C85" s="49">
+      <c r="C85" s="49" t="str">
         <f>IF(C84="","",IF(C84+1&gt;MAX(tblData[Дата]),"",C84+1))</f>
         <v/>
       </c>
     </row>
     <row r="86">
-      <c r="C86" s="49">
+      <c r="C86" s="49" t="str">
         <f>IF(C85="","",IF(C85+1&gt;MAX(tblData[Дата]),"",C85+1))</f>
         <v/>
       </c>
     </row>
     <row r="87">
-      <c r="C87" s="49">
+      <c r="C87" s="49" t="str">
         <f>IF(C86="","",IF(C86+1&gt;MAX(tblData[Дата]),"",C86+1))</f>
         <v/>
       </c>
     </row>
     <row r="88">
-      <c r="C88" s="49">
+      <c r="C88" s="49" t="str">
         <f>IF(C87="","",IF(C87+1&gt;MAX(tblData[Дата]),"",C87+1))</f>
         <v/>
       </c>
     </row>
     <row r="89">
-      <c r="C89" s="49">
+      <c r="C89" s="49" t="str">
         <f>IF(C88="","",IF(C88+1&gt;MAX(tblData[Дата]),"",C88+1))</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="C90" s="49">
+      <c r="C90" s="49" t="str">
         <f>IF(C89="","",IF(C89+1&gt;MAX(tblData[Дата]),"",C89+1))</f>
         <v/>
       </c>
     </row>
     <row r="91">
-      <c r="C91" s="49">
+      <c r="C91" s="49" t="str">
         <f>IF(C90="","",IF(C90+1&gt;MAX(tblData[Дата]),"",C90+1))</f>
         <v/>
       </c>
     </row>
     <row r="92">
-      <c r="C92" s="49">
+      <c r="C92" s="49" t="str">
         <f>IF(C91="","",IF(C91+1&gt;MAX(tblData[Дата]),"",C91+1))</f>
         <v/>
       </c>
     </row>
     <row r="93">
-      <c r="C93" s="49">
+      <c r="C93" s="49" t="str">
         <f>IF(C92="","",IF(C92+1&gt;MAX(tblData[Дата]),"",C92+1))</f>
         <v/>
       </c>
     </row>
     <row r="94">
-      <c r="C94" s="49">
+      <c r="C94" s="49" t="str">
         <f>IF(C93="","",IF(C93+1&gt;MAX(tblData[Дата]),"",C93+1))</f>
         <v/>
       </c>
     </row>
     <row r="95">
-      <c r="C95" s="49">
+      <c r="C95" s="49" t="str">
         <f>IF(C94="","",IF(C94+1&gt;MAX(tblData[Дата]),"",C94+1))</f>
         <v/>
       </c>
     </row>
     <row r="96">
-      <c r="C96" s="49">
+      <c r="C96" s="49" t="str">
         <f>IF(C95="","",IF(C95+1&gt;MAX(tblData[Дата]),"",C95+1))</f>
         <v/>
       </c>
     </row>
     <row r="97">
-      <c r="C97" s="49">
+      <c r="C97" s="49" t="str">
         <f>IF(C96="","",IF(C96+1&gt;MAX(tblData[Дата]),"",C96+1))</f>
         <v/>
       </c>
     </row>
     <row r="98">
-      <c r="C98" s="49">
+      <c r="C98" s="49" t="str">
         <f>IF(C97="","",IF(C97+1&gt;MAX(tblData[Дата]),"",C97+1))</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="C99" s="49">
+      <c r="C99" s="49" t="str">
         <f>IF(C98="","",IF(C98+1&gt;MAX(tblData[Дата]),"",C98+1))</f>
         <v/>
       </c>
     </row>
     <row r="100">
-      <c r="C100" s="49">
+      <c r="C100" s="49" t="str">
         <f>IF(C99="","",IF(C99+1&gt;MAX(tblData[Дата]),"",C99+1))</f>
         <v/>
       </c>
     </row>
     <row r="101">
-      <c r="C101" s="49">
+      <c r="C101" s="49" t="str">
         <f>IF(C100="","",IF(C100+1&gt;MAX(tblData[Дата]),"",C100+1))</f>
         <v/>
       </c>
     </row>
     <row r="102">
-      <c r="C102" s="49">
+      <c r="C102" s="49" t="str">
         <f>IF(C101="","",IF(C101+1&gt;MAX(tblData[Дата]),"",C101+1))</f>
         <v/>
       </c>
     </row>
     <row r="103">
-      <c r="C103" s="49">
+      <c r="C103" s="49" t="str">
         <f>IF(C102="","",IF(C102+1&gt;MAX(tblData[Дата]),"",C102+1))</f>
         <v/>
       </c>
     </row>
     <row r="104">
-      <c r="C104" s="49">
+      <c r="C104" s="49" t="str">
         <f>IF(C103="","",IF(C103+1&gt;MAX(tblData[Дата]),"",C103+1))</f>
         <v/>
       </c>
     </row>
     <row r="105">
-      <c r="C105" s="49">
+      <c r="C105" s="49" t="str">
         <f>IF(C104="","",IF(C104+1&gt;MAX(tblData[Дата]),"",C104+1))</f>
         <v/>
       </c>
     </row>
     <row r="106">
-      <c r="C106" s="49">
+      <c r="C106" s="49" t="str">
         <f>IF(C105="","",IF(C105+1&gt;MAX(tblData[Дата]),"",C105+1))</f>
         <v/>
       </c>
     </row>
     <row r="107">
-      <c r="C107" s="49">
+      <c r="C107" s="49" t="str">
         <f>IF(C106="","",IF(C106+1&gt;MAX(tblData[Дата]),"",C106+1))</f>
         <v/>
       </c>
     </row>
     <row r="108">
-      <c r="C108" s="49">
+      <c r="C108" s="49" t="str">
         <f>IF(C107="","",IF(C107+1&gt;MAX(tblData[Дата]),"",C107+1))</f>
         <v/>
       </c>
     </row>
     <row r="109">
-      <c r="C109" s="49">
+      <c r="C109" s="49" t="str">
         <f>IF(C108="","",IF(C108+1&gt;MAX(tblData[Дата]),"",C108+1))</f>
         <v/>
       </c>
     </row>
     <row r="110">
-      <c r="C110" s="49">
+      <c r="C110" s="49" t="str">
         <f>IF(C109="","",IF(C109+1&gt;MAX(tblData[Дата]),"",C109+1))</f>
         <v/>
       </c>
     </row>
     <row r="111">
-      <c r="C111" s="49">
+      <c r="C111" s="49" t="str">
         <f>IF(C110="","",IF(C110+1&gt;MAX(tblData[Дата]),"",C110+1))</f>
         <v/>
       </c>
     </row>
     <row r="112">
-      <c r="C112" s="49">
+      <c r="C112" s="49" t="str">
         <f>IF(C111="","",IF(C111+1&gt;MAX(tblData[Дата]),"",C111+1))</f>
         <v/>
       </c>
     </row>
     <row r="113">
-      <c r="C113" s="49">
+      <c r="C113" s="49" t="str">
         <f>IF(C112="","",IF(C112+1&gt;MAX(tblData[Дата]),"",C112+1))</f>
         <v/>
       </c>
     </row>
     <row r="114">
-      <c r="C114" s="49">
+      <c r="C114" s="49" t="str">
         <f>IF(C113="","",IF(C113+1&gt;MAX(tblData[Дата]),"",C113+1))</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="C115" s="49">
+      <c r="C115" s="49" t="str">
         <f>IF(C114="","",IF(C114+1&gt;MAX(tblData[Дата]),"",C114+1))</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="C116" s="49">
+      <c r="C116" s="49" t="str">
         <f>IF(C115="","",IF(C115+1&gt;MAX(tblData[Дата]),"",C115+1))</f>
         <v/>
       </c>
     </row>
     <row r="117">
-      <c r="C117" s="49">
+      <c r="C117" s="49" t="str">
         <f>IF(C116="","",IF(C116+1&gt;MAX(tblData[Дата]),"",C116+1))</f>
         <v/>
       </c>
     </row>
     <row r="118">
-      <c r="C118" s="49">
+      <c r="C118" s="49" t="str">
         <f>IF(C117="","",IF(C117+1&gt;MAX(tblData[Дата]),"",C117+1))</f>
         <v/>
       </c>
     </row>
     <row r="119">
-      <c r="C119" s="49">
+      <c r="C119" s="49" t="str">
         <f>IF(C118="","",IF(C118+1&gt;MAX(tblData[Дата]),"",C118+1))</f>
         <v/>
       </c>
     </row>
     <row r="120">
-      <c r="C120" s="49">
+      <c r="C120" s="49" t="str">
         <f>IF(C119="","",IF(C119+1&gt;MAX(tblData[Дата]),"",C119+1))</f>
         <v/>
       </c>
     </row>
     <row r="121">
-      <c r="C121" s="49">
+      <c r="C121" s="49" t="str">
         <f>IF(C120="","",IF(C120+1&gt;MAX(tblData[Дата]),"",C120+1))</f>
         <v/>
       </c>
     </row>
     <row r="122">
-      <c r="C122" s="49">
+      <c r="C122" s="49" t="str">
         <f>IF(C121="","",IF(C121+1&gt;MAX(tblData[Дата]),"",C121+1))</f>
         <v/>
       </c>
     </row>
     <row r="123">
-      <c r="C123" s="49">
+      <c r="C123" s="49" t="str">
         <f>IF(C122="","",IF(C122+1&gt;MAX(tblData[Дата]),"",C122+1))</f>
         <v/>
       </c>
     </row>
     <row r="124">
-      <c r="C124" s="49">
+      <c r="C124" s="49" t="str">
         <f>IF(C123="","",IF(C123+1&gt;MAX(tblData[Дата]),"",C123+1))</f>
         <v/>
       </c>
     </row>
     <row r="125">
-      <c r="C125" s="49">
+      <c r="C125" s="49" t="str">
         <f>IF(C124="","",IF(C124+1&gt;MAX(tblData[Дата]),"",C124+1))</f>
         <v/>
       </c>
     </row>
     <row r="126">
-      <c r="C126" s="49">
+      <c r="C126" s="49" t="str">
         <f>IF(C125="","",IF(C125+1&gt;MAX(tblData[Дата]),"",C125+1))</f>
         <v/>
       </c>
     </row>
     <row r="127">
-      <c r="C127" s="49">
+      <c r="C127" s="49" t="str">
         <f>IF(C126="","",IF(C126+1&gt;MAX(tblData[Дата]),"",C126+1))</f>
         <v/>
       </c>
     </row>
     <row r="128">
-      <c r="C128" s="49">
+      <c r="C128" s="49" t="str">
         <f>IF(C127="","",IF(C127+1&gt;MAX(tblData[Дата]),"",C127+1))</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="C129" s="49">
+      <c r="C129" s="49" t="str">
         <f>IF(C128="","",IF(C128+1&gt;MAX(tblData[Дата]),"",C128+1))</f>
         <v/>
       </c>
     </row>
     <row r="130">
-      <c r="C130" s="49">
+      <c r="C130" s="49" t="str">
         <f>IF(C129="","",IF(C129+1&gt;MAX(tblData[Дата]),"",C129+1))</f>
         <v/>
       </c>
     </row>
     <row r="131">
-      <c r="C131" s="49">
+      <c r="C131" s="49" t="str">
         <f>IF(C130="","",IF(C130+1&gt;MAX(tblData[Дата]),"",C130+1))</f>
         <v/>
       </c>
     </row>
     <row r="132">
-      <c r="C132" s="49">
+      <c r="C132" s="49" t="str">
         <f>IF(C131="","",IF(C131+1&gt;MAX(tblData[Дата]),"",C131+1))</f>
         <v/>
       </c>
     </row>
     <row r="133">
-      <c r="C133" s="49">
+      <c r="C133" s="49" t="str">
         <f>IF(C132="","",IF(C132+1&gt;MAX(tblData[Дата]),"",C132+1))</f>
         <v/>
       </c>
     </row>
     <row r="134">
-      <c r="C134" s="49">
+      <c r="C134" s="49" t="str">
         <f>IF(C133="","",IF(C133+1&gt;MAX(tblData[Дата]),"",C133+1))</f>
         <v/>
       </c>
     </row>
     <row r="135">
-      <c r="C135" s="49">
+      <c r="C135" s="49" t="str">
         <f>IF(C134="","",IF(C134+1&gt;MAX(tblData[Дата]),"",C134+1))</f>
         <v/>
       </c>
     </row>
     <row r="136">
-      <c r="C136" s="49">
+      <c r="C136" s="49" t="str">
         <f>IF(C135="","",IF(C135+1&gt;MAX(tblData[Дата]),"",C135+1))</f>
         <v/>
       </c>
     </row>
     <row r="137">
-      <c r="C137" s="49">
+      <c r="C137" s="49" t="str">
         <f>IF(C136="","",IF(C136+1&gt;MAX(tblData[Дата]),"",C136+1))</f>
         <v/>
       </c>
     </row>
     <row r="138">
-      <c r="C138" s="49">
+      <c r="C138" s="49" t="str">
         <f>IF(C137="","",IF(C137+1&gt;MAX(tblData[Дата]),"",C137+1))</f>
         <v/>
       </c>
     </row>
     <row r="139">
-      <c r="C139" s="49">
+      <c r="C139" s="49" t="str">
         <f>IF(C138="","",IF(C138+1&gt;MAX(tblData[Дата]),"",C138+1))</f>
         <v/>
       </c>
     </row>
     <row r="140">
-      <c r="C140" s="49">
+      <c r="C140" s="49" t="str">
         <f>IF(C139="","",IF(C139+1&gt;MAX(tblData[Дата]),"",C139+1))</f>
         <v/>
       </c>
     </row>
     <row r="141">
-      <c r="C141" s="49">
+      <c r="C141" s="49" t="str">
         <f>IF(C140="","",IF(C140+1&gt;MAX(tblData[Дата]),"",C140+1))</f>
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="C142" s="49">
+      <c r="C142" s="49" t="str">
         <f>IF(C141="","",IF(C141+1&gt;MAX(tblData[Дата]),"",C141+1))</f>
         <v/>
       </c>
     </row>
     <row r="143">
-      <c r="C143" s="49">
+      <c r="C143" s="49" t="str">
         <f>IF(C142="","",IF(C142+1&gt;MAX(tblData[Дата]),"",C142+1))</f>
         <v/>
       </c>
     </row>
     <row r="144">
-      <c r="C144" s="49">
+      <c r="C144" s="49" t="str">
         <f>IF(C143="","",IF(C143+1&gt;MAX(tblData[Дата]),"",C143+1))</f>
         <v/>
       </c>
     </row>
     <row r="145">
-      <c r="C145" s="49">
+      <c r="C145" s="49" t="str">
         <f>IF(C144="","",IF(C144+1&gt;MAX(tblData[Дата]),"",C144+1))</f>
         <v/>
       </c>
     </row>
     <row r="146">
-      <c r="C146" s="49">
+      <c r="C146" s="49" t="str">
         <f>IF(C145="","",IF(C145+1&gt;MAX(tblData[Дата]),"",C145+1))</f>
         <v/>
       </c>
     </row>
     <row r="147">
-      <c r="C147" s="49">
+      <c r="C147" s="49" t="str">
         <f>IF(C146="","",IF(C146+1&gt;MAX(tblData[Дата]),"",C146+1))</f>
         <v/>
       </c>
     </row>
     <row r="148">
-      <c r="C148" s="49">
+      <c r="C148" s="49" t="str">
         <f>IF(C147="","",IF(C147+1&gt;MAX(tblData[Дата]),"",C147+1))</f>
         <v/>
       </c>
     </row>
     <row r="149">
-      <c r="C149" s="49">
+      <c r="C149" s="49" t="str">
         <f>IF(C148="","",IF(C148+1&gt;MAX(tblData[Дата]),"",C148+1))</f>
         <v/>
       </c>
     </row>
     <row r="150">
-      <c r="C150" s="49">
+      <c r="C150" s="49" t="str">
         <f>IF(C149="","",IF(C149+1&gt;MAX(tblData[Дата]),"",C149+1))</f>
         <v/>
       </c>
     </row>
     <row r="151">
-      <c r="C151" s="49">
+      <c r="C151" s="49" t="str">
         <f>IF(C150="","",IF(C150+1&gt;MAX(tblData[Дата]),"",C150+1))</f>
         <v/>
       </c>
     </row>
     <row r="152">
-      <c r="C152" s="49">
+      <c r="C152" s="49" t="str">
         <f>IF(C151="","",IF(C151+1&gt;MAX(tblData[Дата]),"",C151+1))</f>
         <v/>
       </c>
     </row>
     <row r="153">
-      <c r="C153" s="49">
+      <c r="C153" s="49" t="str">
         <f>IF(C152="","",IF(C152+1&gt;MAX(tblData[Дата]),"",C152+1))</f>
         <v/>
       </c>
     </row>
     <row r="154">
-      <c r="C154" s="49">
+      <c r="C154" s="49" t="str">
         <f>IF(C153="","",IF(C153+1&gt;MAX(tblData[Дата]),"",C153+1))</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="C155" s="49">
+      <c r="C155" s="49" t="str">
         <f>IF(C154="","",IF(C154+1&gt;MAX(tblData[Дата]),"",C154+1))</f>
         <v/>
       </c>
     </row>
     <row r="156">
-      <c r="C156" s="49">
+      <c r="C156" s="49" t="str">
         <f>IF(C155="","",IF(C155+1&gt;MAX(tblData[Дата]),"",C155+1))</f>
         <v/>
       </c>
     </row>
     <row r="157">
-      <c r="C157" s="49">
+      <c r="C157" s="49" t="str">
         <f>IF(C156="","",IF(C156+1&gt;MAX(tblData[Дата]),"",C156+1))</f>
         <v/>
       </c>
     </row>
     <row r="158">
-      <c r="C158" s="49">
+      <c r="C158" s="49" t="str">
         <f>IF(C157="","",IF(C157+1&gt;MAX(tblData[Дата]),"",C157+1))</f>
         <v/>
       </c>
     </row>
     <row r="159">
-      <c r="C159" s="49">
+      <c r="C159" s="49" t="str">
         <f>IF(C158="","",IF(C158+1&gt;MAX(tblData[Дата]),"",C158+1))</f>
         <v/>
       </c>
     </row>
     <row r="160">
-      <c r="C160" s="49">
+      <c r="C160" s="49" t="str">
         <f>IF(C159="","",IF(C159+1&gt;MAX(tblData[Дата]),"",C159+1))</f>
         <v/>
       </c>
     </row>
     <row r="161">
-      <c r="C161" s="49">
+      <c r="C161" s="49" t="str">
         <f>IF(C160="","",IF(C160+1&gt;MAX(tblData[Дата]),"",C160+1))</f>
         <v/>
       </c>
     </row>
     <row r="162">
-      <c r="C162" s="49">
+      <c r="C162" s="49" t="str">
         <f>IF(C161="","",IF(C161+1&gt;MAX(tblData[Дата]),"",C161+1))</f>
         <v/>
       </c>
     </row>
     <row r="163">
-      <c r="C163" s="49">
+      <c r="C163" s="49" t="str">
         <f>IF(C162="","",IF(C162+1&gt;MAX(tblData[Дата]),"",C162+1))</f>
         <v/>
       </c>
     </row>
     <row r="164">
-      <c r="C164" s="49">
+      <c r="C164" s="49" t="str">
         <f>IF(C163="","",IF(C163+1&gt;MAX(tblData[Дата]),"",C163+1))</f>
         <v/>
       </c>
     </row>
     <row r="165">
-      <c r="C165" s="49">
+      <c r="C165" s="49" t="str">
         <f>IF(C164="","",IF(C164+1&gt;MAX(tblData[Дата]),"",C164+1))</f>
         <v/>
       </c>
     </row>
     <row r="166">
-      <c r="C166" s="49">
+      <c r="C166" s="49" t="str">
         <f>IF(C165="","",IF(C165+1&gt;MAX(tblData[Дата]),"",C165+1))</f>
         <v/>
       </c>
     </row>
     <row r="167">
-      <c r="C167" s="49">
+      <c r="C167" s="49" t="str">
         <f>IF(C166="","",IF(C166+1&gt;MAX(tblData[Дата]),"",C166+1))</f>
         <v/>
       </c>
     </row>
     <row r="168">
-      <c r="C168" s="49">
+      <c r="C168" s="49" t="str">
         <f>IF(C167="","",IF(C167+1&gt;MAX(tblData[Дата]),"",C167+1))</f>
         <v/>
       </c>
     </row>
     <row r="169">
-      <c r="C169" s="49">
+      <c r="C169" s="49" t="str">
         <f>IF(C168="","",IF(C168+1&gt;MAX(tblData[Дата]),"",C168+1))</f>
         <v/>
       </c>
     </row>
     <row r="170">
-      <c r="C170" s="49">
+      <c r="C170" s="49" t="str">
         <f>IF(C169="","",IF(C169+1&gt;MAX(tblData[Дата]),"",C169+1))</f>
         <v/>
       </c>
     </row>
     <row r="171">
-      <c r="C171" s="49">
+      <c r="C171" s="49" t="str">
         <f>IF(C170="","",IF(C170+1&gt;MAX(tblData[Дата]),"",C170+1))</f>
         <v/>
       </c>
     </row>
     <row r="172">
-      <c r="C172" s="49">
+      <c r="C172" s="49" t="str">
         <f>IF(C171="","",IF(C171+1&gt;MAX(tblData[Дата]),"",C171+1))</f>
         <v/>
       </c>
     </row>
     <row r="173">
-      <c r="C173" s="49">
+      <c r="C173" s="49" t="str">
         <f>IF(C172="","",IF(C172+1&gt;MAX(tblData[Дата]),"",C172+1))</f>
         <v/>
       </c>
     </row>
     <row r="174">
-      <c r="C174" s="49">
+      <c r="C174" s="49" t="str">
         <f>IF(C173="","",IF(C173+1&gt;MAX(tblData[Дата]),"",C173+1))</f>
         <v/>
       </c>
     </row>
     <row r="175">
-      <c r="C175" s="49">
+      <c r="C175" s="49" t="str">
         <f>IF(C174="","",IF(C174+1&gt;MAX(tblData[Дата]),"",C174+1))</f>
         <v/>
       </c>
     </row>
     <row r="176">
-      <c r="C176" s="49">
+      <c r="C176" s="49" t="str">
         <f>IF(C175="","",IF(C175+1&gt;MAX(tblData[Дата]),"",C175+1))</f>
         <v/>
       </c>
     </row>
     <row r="177">
-      <c r="C177" s="49">
+      <c r="C177" s="49" t="str">
         <f>IF(C176="","",IF(C176+1&gt;MAX(tblData[Дата]),"",C176+1))</f>
         <v/>
       </c>
     </row>
     <row r="178">
-      <c r="C178" s="49">
+      <c r="C178" s="49" t="str">
         <f>IF(C177="","",IF(C177+1&gt;MAX(tblData[Дата]),"",C177+1))</f>
         <v/>
       </c>
     </row>
     <row r="179">
-      <c r="C179" s="49">
+      <c r="C179" s="49" t="str">
         <f>IF(C178="","",IF(C178+1&gt;MAX(tblData[Дата]),"",C178+1))</f>
         <v/>
       </c>
     </row>
     <row r="180">
-      <c r="C180" s="49">
+      <c r="C180" s="49" t="str">
         <f>IF(C179="","",IF(C179+1&gt;MAX(tblData[Дата]),"",C179+1))</f>
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="C181" s="49">
+      <c r="C181" s="49" t="str">
         <f>IF(C180="","",IF(C180+1&gt;MAX(tblData[Дата]),"",C180+1))</f>
         <v/>
       </c>
     </row>
     <row r="182">
-      <c r="C182" s="49">
+      <c r="C182" s="49" t="str">
         <f>IF(C181="","",IF(C181+1&gt;MAX(tblData[Дата]),"",C181+1))</f>
         <v/>
       </c>
     </row>
     <row r="183">
-      <c r="C183" s="49">
+      <c r="C183" s="49" t="str">
         <f>IF(C182="","",IF(C182+1&gt;MAX(tblData[Дата]),"",C182+1))</f>
         <v/>
       </c>
     </row>
     <row r="184">
-      <c r="C184" s="49">
+      <c r="C184" s="49" t="str">
         <f>IF(C183="","",IF(C183+1&gt;MAX(tblData[Дата]),"",C183+1))</f>
         <v/>
       </c>
     </row>
     <row r="185">
-      <c r="C185" s="49">
+      <c r="C185" s="49" t="str">
         <f>IF(C184="","",IF(C184+1&gt;MAX(tblData[Дата]),"",C184+1))</f>
         <v/>
       </c>
     </row>
     <row r="186">
-      <c r="C186" s="49">
+      <c r="C186" s="49" t="str">
         <f>IF(C185="","",IF(C185+1&gt;MAX(tblData[Дата]),"",C185+1))</f>
         <v/>
       </c>
     </row>
     <row r="187">
-      <c r="C187" s="49">
+      <c r="C187" s="49" t="str">
         <f>IF(C186="","",IF(C186+1&gt;MAX(tblData[Дата]),"",C186+1))</f>
         <v/>
       </c>
     </row>
     <row r="188">
-      <c r="C188" s="49">
+      <c r="C188" s="49" t="str">
         <f>IF(C187="","",IF(C187+1&gt;MAX(tblData[Дата]),"",C187+1))</f>
         <v/>
       </c>
     </row>
     <row r="189">
-      <c r="C189" s="49">
+      <c r="C189" s="49" t="str">
         <f>IF(C188="","",IF(C188+1&gt;MAX(tblData[Дата]),"",C188+1))</f>
         <v/>
       </c>
     </row>
     <row r="190">
-      <c r="C190" s="49">
+      <c r="C190" s="49" t="str">
         <f>IF(C189="","",IF(C189+1&gt;MAX(tblData[Дата]),"",C189+1))</f>
         <v/>
       </c>
     </row>
     <row r="191">
-      <c r="C191" s="49">
+      <c r="C191" s="49" t="str">
         <f>IF(C190="","",IF(C190+1&gt;MAX(tblData[Дата]),"",C190+1))</f>
         <v/>
       </c>
     </row>
     <row r="192">
-      <c r="C192" s="49">
+      <c r="C192" s="49" t="str">
         <f>IF(C191="","",IF(C191+1&gt;MAX(tblData[Дата]),"",C191+1))</f>
         <v/>
       </c>
     </row>
     <row r="193">
-      <c r="C193" s="49">
+      <c r="C193" s="49" t="str">
         <f>IF(C192="","",IF(C192+1&gt;MAX(tblData[Дата]),"",C192+1))</f>
         <v/>
       </c>
     </row>
     <row r="194">
-      <c r="C194" s="49">
+      <c r="C194" s="49" t="str">
         <f>IF(C193="","",IF(C193+1&gt;MAX(tblData[Дата]),"",C193+1))</f>
         <v/>
       </c>
     </row>
     <row r="195">
-      <c r="C195" s="49">
+      <c r="C195" s="49" t="str">
         <f>IF(C194="","",IF(C194+1&gt;MAX(tblData[Дата]),"",C194+1))</f>
         <v/>
       </c>
     </row>
     <row r="196">
-      <c r="C196" s="49">
+      <c r="C196" s="49" t="str">
         <f>IF(C195="","",IF(C195+1&gt;MAX(tblData[Дата]),"",C195+1))</f>
         <v/>
       </c>
     </row>
     <row r="197">
-      <c r="C197" s="49">
+      <c r="C197" s="49" t="str">
         <f>IF(C196="","",IF(C196+1&gt;MAX(tblData[Дата]),"",C196+1))</f>
         <v/>
       </c>
     </row>
     <row r="198">
-      <c r="C198" s="49">
+      <c r="C198" s="49" t="str">
         <f>IF(C197="","",IF(C197+1&gt;MAX(tblData[Дата]),"",C197+1))</f>
         <v/>
       </c>
     </row>
     <row r="199">
-      <c r="C199" s="49">
+      <c r="C199" s="49" t="str">
         <f>IF(C198="","",IF(C198+1&gt;MAX(tblData[Дата]),"",C198+1))</f>
         <v/>
       </c>
     </row>
     <row r="200">
-      <c r="C200" s="49">
+      <c r="C200" s="49" t="str">
         <f>IF(C199="","",IF(C199+1&gt;MAX(tblData[Дата]),"",C199+1))</f>
         <v/>
       </c>
     </row>
     <row r="201">
-      <c r="C201" s="49">
+      <c r="C201" s="49" t="str">
         <f>IF(C200="","",IF(C200+1&gt;MAX(tblData[Дата]),"",C200+1))</f>
         <v/>
       </c>
     </row>
     <row r="202">
-      <c r="C202" s="49">
+      <c r="C202" s="49" t="str">
         <f>IF(C201="","",IF(C201+1&gt;MAX(tblData[Дата]),"",C201+1))</f>
         <v/>
       </c>
     </row>
     <row r="203">
-      <c r="C203" s="49">
+      <c r="C203" s="49" t="str">
         <f>IF(C202="","",IF(C202+1&gt;MAX(tblData[Дата]),"",C202+1))</f>
         <v/>
       </c>
     </row>
     <row r="204">
-      <c r="C204" s="49">
+      <c r="C204" s="49" t="str">
         <f>IF(C203="","",IF(C203+1&gt;MAX(tblData[Дата]),"",C203+1))</f>
         <v/>
       </c>
     </row>
     <row r="205">
-      <c r="C205" s="49">
+      <c r="C205" s="49" t="str">
         <f>IF(C204="","",IF(C204+1&gt;MAX(tblData[Дата]),"",C204+1))</f>
         <v/>
       </c>
     </row>
     <row r="206">
-      <c r="C206" s="49">
+      <c r="C206" s="49" t="str">
         <f>IF(C205="","",IF(C205+1&gt;MAX(tblData[Дата]),"",C205+1))</f>
         <v/>
       </c>
     </row>
     <row r="207">
-      <c r="C207" s="49">
+      <c r="C207" s="49" t="str">
         <f>IF(C206="","",IF(C206+1&gt;MAX(tblData[Дата]),"",C206+1))</f>
         <v/>
       </c>
     </row>
     <row r="208">
-      <c r="C208" s="49">
+      <c r="C208" s="49" t="str">
         <f>IF(C207="","",IF(C207+1&gt;MAX(tblData[Дата]),"",C207+1))</f>
         <v/>
       </c>
     </row>
     <row r="209">
-      <c r="C209" s="49">
+      <c r="C209" s="49" t="str">
         <f>IF(C208="","",IF(C208+1&gt;MAX(tblData[Дата]),"",C208+1))</f>
         <v/>
       </c>
     </row>
     <row r="210">
-      <c r="C210" s="49">
+      <c r="C210" s="49" t="str">
         <f>IF(C209="","",IF(C209+1&gt;MAX(tblData[Дата]),"",C209+1))</f>
         <v/>
       </c>
     </row>
     <row r="211">
-      <c r="C211" s="49">
+      <c r="C211" s="49" t="str">
         <f>IF(C210="","",IF(C210+1&gt;MAX(tblData[Дата]),"",C210+1))</f>
         <v/>
       </c>
     </row>
     <row r="212">
-      <c r="C212" s="49">
+      <c r="C212" s="49" t="str">
         <f>IF(C211="","",IF(C211+1&gt;MAX(tblData[Дата]),"",C211+1))</f>
         <v/>
       </c>
     </row>
     <row r="213">
-      <c r="C213" s="49">
+      <c r="C213" s="49" t="str">
         <f>IF(C212="","",IF(C212+1&gt;MAX(tblData[Дата]),"",C212+1))</f>
         <v/>
       </c>
     </row>
     <row r="214">
-      <c r="C214" s="49">
+      <c r="C214" s="49" t="str">
         <f>IF(C213="","",IF(C213+1&gt;MAX(tblData[Дата]),"",C213+1))</f>
         <v/>
       </c>
     </row>
     <row r="215">
-      <c r="C215" s="49">
+      <c r="C215" s="49" t="str">
         <f>IF(C214="","",IF(C214+1&gt;MAX(tblData[Дата]),"",C214+1))</f>
         <v/>
       </c>
     </row>
     <row r="216">
-      <c r="C216" s="49">
+      <c r="C216" s="49" t="str">
         <f>IF(C215="","",IF(C215+1&gt;MAX(tblData[Дата]),"",C215+1))</f>
         <v/>
       </c>
     </row>
     <row r="217">
-      <c r="C217" s="49">
+      <c r="C217" s="49" t="str">
         <f>IF(C216="","",IF(C216+1&gt;MAX(tblData[Дата]),"",C216+1))</f>
         <v/>
       </c>
     </row>
     <row r="218">
-      <c r="C218" s="49">
+      <c r="C218" s="49" t="str">
         <f>IF(C217="","",IF(C217+1&gt;MAX(tblData[Дата]),"",C217+1))</f>
         <v/>
       </c>
     </row>
     <row r="219">
-      <c r="C219" s="49">
+      <c r="C219" s="49" t="str">
         <f>IF(C218="","",IF(C218+1&gt;MAX(tblData[Дата]),"",C218+1))</f>
         <v/>
       </c>
     </row>
     <row r="220">
-      <c r="C220" s="49">
+      <c r="C220" s="49" t="str">
         <f>IF(C219="","",IF(C219+1&gt;MAX(tblData[Дата]),"",C219+1))</f>
         <v/>
       </c>
     </row>
     <row r="221">
-      <c r="C221" s="49">
+      <c r="C221" s="49" t="str">
         <f>IF(C220="","",IF(C220+1&gt;MAX(tblData[Дата]),"",C220+1))</f>
         <v/>
       </c>
     </row>
     <row r="222">
-      <c r="C222" s="49">
+      <c r="C222" s="49" t="str">
         <f>IF(C221="","",IF(C221+1&gt;MAX(tblData[Дата]),"",C221+1))</f>
         <v/>
       </c>
     </row>
     <row r="223">
-      <c r="C223" s="49">
+      <c r="C223" s="49" t="str">
         <f>IF(C222="","",IF(C222+1&gt;MAX(tblData[Дата]),"",C222+1))</f>
         <v/>
       </c>
     </row>
     <row r="224">
-      <c r="C224" s="49">
+      <c r="C224" s="49" t="str">
         <f>IF(C223="","",IF(C223+1&gt;MAX(tblData[Дата]),"",C223+1))</f>
         <v/>
       </c>
     </row>
     <row r="225">
-      <c r="C225" s="49">
+      <c r="C225" s="49" t="str">
         <f>IF(C224="","",IF(C224+1&gt;MAX(tblData[Дата]),"",C224+1))</f>
         <v/>
       </c>
     </row>
     <row r="226">
-      <c r="C226" s="49">
+      <c r="C226" s="49" t="str">
         <f>IF(C225="","",IF(C225+1&gt;MAX(tblData[Дата]),"",C225+1))</f>
         <v/>
       </c>
     </row>
     <row r="227">
-      <c r="C227" s="49">
+      <c r="C227" s="49" t="str">
         <f>IF(C226="","",IF(C226+1&gt;MAX(tblData[Дата]),"",C226+1))</f>
         <v/>
       </c>
     </row>
     <row r="228">
-      <c r="C228" s="49">
+      <c r="C228" s="49" t="str">
         <f>IF(C227="","",IF(C227+1&gt;MAX(tblData[Дата]),"",C227+1))</f>
         <v/>
       </c>
     </row>
     <row r="229">
-      <c r="C229" s="49">
+      <c r="C229" s="49" t="str">
         <f>IF(C228="","",IF(C228+1&gt;MAX(tblData[Дата]),"",C228+1))</f>
         <v/>
       </c>
     </row>
     <row r="230">
-      <c r="C230" s="49">
+      <c r="C230" s="49" t="str">
         <f>IF(C229="","",IF(C229+1&gt;MAX(tblData[Дата]),"",C229+1))</f>
         <v/>
       </c>
     </row>
     <row r="231">
-      <c r="C231" s="49">
+      <c r="C231" s="49" t="str">
         <f>IF(C230="","",IF(C230+1&gt;MAX(tblData[Дата]),"",C230+1))</f>
         <v/>
       </c>
     </row>
     <row r="232">
-      <c r="C232" s="49">
+      <c r="C232" s="49" t="str">
         <f>IF(C231="","",IF(C231+1&gt;MAX(tblData[Дата]),"",C231+1))</f>
         <v/>
       </c>
     </row>
     <row r="233">
-      <c r="C233" s="49">
+      <c r="C233" s="49" t="str">
         <f>IF(C232="","",IF(C232+1&gt;MAX(tblData[Дата]),"",C232+1))</f>
         <v/>
       </c>
     </row>
     <row r="234">
-      <c r="C234" s="49">
+      <c r="C234" s="49" t="str">
         <f>IF(C233="","",IF(C233+1&gt;MAX(tblData[Дата]),"",C233+1))</f>
         <v/>
       </c>
     </row>
     <row r="235">
-      <c r="C235" s="49">
+      <c r="C235" s="49" t="str">
         <f>IF(C234="","",IF(C234+1&gt;MAX(tblData[Дата]),"",C234+1))</f>
         <v/>
       </c>
     </row>
     <row r="236">
-      <c r="C236" s="49">
+      <c r="C236" s="49" t="str">
         <f>IF(C235="","",IF(C235+1&gt;MAX(tblData[Дата]),"",C235+1))</f>
         <v/>
       </c>
     </row>
     <row r="237">
-      <c r="C237" s="49">
+      <c r="C237" s="49" t="str">
         <f>IF(C236="","",IF(C236+1&gt;MAX(tblData[Дата]),"",C236+1))</f>
         <v/>
       </c>
     </row>
     <row r="238">
-      <c r="C238" s="49">
+      <c r="C238" s="49" t="str">
         <f>IF(C237="","",IF(C237+1&gt;MAX(tblData[Дата]),"",C237+1))</f>
         <v/>
       </c>
     </row>
     <row r="239">
-      <c r="C239" s="49">
+      <c r="C239" s="49" t="str">
         <f>IF(C238="","",IF(C238+1&gt;MAX(tblData[Дата]),"",C238+1))</f>
         <v/>
       </c>
     </row>
     <row r="240">
-      <c r="C240" s="49">
+      <c r="C240" s="49" t="str">
         <f>IF(C239="","",IF(C239+1&gt;MAX(tblData[Дата]),"",C239+1))</f>
         <v/>
       </c>
     </row>
     <row r="241">
-      <c r="C241" s="49">
+      <c r="C241" s="49" t="str">
         <f>IF(C240="","",IF(C240+1&gt;MAX(tblData[Дата]),"",C240+1))</f>
         <v/>
       </c>
     </row>
     <row r="242">
-      <c r="C242" s="49">
+      <c r="C242" s="49" t="str">
         <f>IF(C241="","",IF(C241+1&gt;MAX(tblData[Дата]),"",C241+1))</f>
         <v/>
       </c>
     </row>
     <row r="243">
-      <c r="C243" s="49">
+      <c r="C243" s="49" t="str">
         <f>IF(C242="","",IF(C242+1&gt;MAX(tblData[Дата]),"",C242+1))</f>
         <v/>
       </c>
     </row>
     <row r="244">
-      <c r="C244" s="49">
+      <c r="C244" s="49" t="str">
         <f>IF(C243="","",IF(C243+1&gt;MAX(tblData[Дата]),"",C243+1))</f>
         <v/>
       </c>
     </row>
     <row r="245">
-      <c r="C245" s="49">
+      <c r="C245" s="49" t="str">
         <f>IF(C244="","",IF(C244+1&gt;MAX(tblData[Дата]),"",C244+1))</f>
         <v/>
       </c>
     </row>
     <row r="246">
-      <c r="C246" s="49">
+      <c r="C246" s="49" t="str">
         <f>IF(C245="","",IF(C245+1&gt;MAX(tblData[Дата]),"",C245+1))</f>
         <v/>
       </c>
     </row>
     <row r="247">
-      <c r="C247" s="49">
+      <c r="C247" s="49" t="str">
         <f>IF(C246="","",IF(C246+1&gt;MAX(tblData[Дата]),"",C246+1))</f>
         <v/>
       </c>
     </row>
     <row r="248">
-      <c r="C248" s="49">
+      <c r="C248" s="49" t="str">
         <f>IF(C247="","",IF(C247+1&gt;MAX(tblData[Дата]),"",C247+1))</f>
         <v/>
       </c>
     </row>
     <row r="249">
-      <c r="C249" s="49">
+      <c r="C249" s="49" t="str">
         <f>IF(C248="","",IF(C248+1&gt;MAX(tblData[Дата]),"",C248+1))</f>
         <v/>
       </c>
     </row>
     <row r="250">
-      <c r="C250" s="49">
+      <c r="C250" s="49" t="str">
         <f>IF(C249="","",IF(C249+1&gt;MAX(tblData[Дата]),"",C249+1))</f>
         <v/>
       </c>
     </row>
     <row r="251">
-      <c r="C251" s="49">
+      <c r="C251" s="49" t="str">
         <f>IF(C250="","",IF(C250+1&gt;MAX(tblData[Дата]),"",C250+1))</f>
         <v/>
       </c>
     </row>
     <row r="252">
-      <c r="C252" s="49">
+      <c r="C252" s="49" t="str">
         <f>IF(C251="","",IF(C251+1&gt;MAX(tblData[Дата]),"",C251+1))</f>
         <v/>
       </c>
     </row>
     <row r="253">
-      <c r="C253" s="49">
+      <c r="C253" s="49" t="str">
         <f>IF(C252="","",IF(C252+1&gt;MAX(tblData[Дата]),"",C252+1))</f>
         <v/>
       </c>
     </row>
     <row r="254">
-      <c r="C254" s="49">
+      <c r="C254" s="49" t="str">
         <f>IF(C253="","",IF(C253+1&gt;MAX(tblData[Дата]),"",C253+1))</f>
         <v/>
       </c>
     </row>
     <row r="255">
-      <c r="C255" s="49">
+      <c r="C255" s="49" t="str">
         <f>IF(C254="","",IF(C254+1&gt;MAX(tblData[Дата]),"",C254+1))</f>
         <v/>
       </c>
     </row>
     <row r="256">
-      <c r="C256" s="49">
+      <c r="C256" s="49" t="str">
         <f>IF(C255="","",IF(C255+1&gt;MAX(tblData[Дата]),"",C255+1))</f>
         <v/>
       </c>
     </row>
     <row r="257">
-      <c r="C257" s="49">
+      <c r="C257" s="49" t="str">
         <f>IF(C256="","",IF(C256+1&gt;MAX(tblData[Дата]),"",C256+1))</f>
         <v/>
       </c>
     </row>
     <row r="258">
-      <c r="C258" s="49">
+      <c r="C258" s="49" t="str">
         <f>IF(C257="","",IF(C257+1&gt;MAX(tblData[Дата]),"",C257+1))</f>
         <v/>
       </c>
     </row>
     <row r="259">
-      <c r="C259" s="49">
+      <c r="C259" s="49" t="str">
         <f>IF(C258="","",IF(C258+1&gt;MAX(tblData[Дата]),"",C258+1))</f>
         <v/>
       </c>
     </row>
     <row r="260">
-      <c r="C260" s="49">
+      <c r="C260" s="49" t="str">
         <f>IF(C259="","",IF(C259+1&gt;MAX(tblData[Дата]),"",C259+1))</f>
         <v/>
       </c>
     </row>
     <row r="261">
-      <c r="C261" s="49">
+      <c r="C261" s="49" t="str">
         <f>IF(C260="","",IF(C260+1&gt;MAX(tblData[Дата]),"",C260+1))</f>
         <v/>
       </c>
     </row>
     <row r="262">
-      <c r="C262" s="49">
+      <c r="C262" s="49" t="str">
         <f>IF(C261="","",IF(C261+1&gt;MAX(tblData[Дата]),"",C261+1))</f>
         <v/>
       </c>
     </row>
     <row r="263">
-      <c r="C263" s="49">
+      <c r="C263" s="49" t="str">
         <f>IF(C262="","",IF(C262+1&gt;MAX(tblData[Дата]),"",C262+1))</f>
         <v/>
       </c>
     </row>
     <row r="264">
-      <c r="C264" s="49">
+      <c r="C264" s="49" t="str">
         <f>IF(C263="","",IF(C263+1&gt;MAX(tblData[Дата]),"",C263+1))</f>
         <v/>
       </c>
     </row>
     <row r="265">
-      <c r="C265" s="49">
+      <c r="C265" s="49" t="str">
         <f>IF(C264="","",IF(C264+1&gt;MAX(tblData[Дата]),"",C264+1))</f>
         <v/>
       </c>
     </row>
     <row r="266">
-      <c r="C266" s="49">
+      <c r="C266" s="49" t="str">
         <f>IF(C265="","",IF(C265+1&gt;MAX(tblData[Дата]),"",C265+1))</f>
         <v/>
       </c>
     </row>
     <row r="267">
-      <c r="C267" s="49">
+      <c r="C267" s="49" t="str">
         <f>IF(C266="","",IF(C266+1&gt;MAX(tblData[Дата]),"",C266+1))</f>
         <v/>
       </c>
     </row>
     <row r="268">
-      <c r="C268" s="49">
+      <c r="C268" s="49" t="str">
         <f>IF(C267="","",IF(C267+1&gt;MAX(tblData[Дата]),"",C267+1))</f>
         <v/>
       </c>
     </row>
     <row r="269">
-      <c r="C269" s="49">
+      <c r="C269" s="49" t="str">
         <f>IF(C268="","",IF(C268+1&gt;MAX(tblData[Дата]),"",C268+1))</f>
         <v/>
       </c>
     </row>
     <row r="270">
-      <c r="C270" s="49">
+      <c r="C270" s="49" t="str">
         <f>IF(C269="","",IF(C269+1&gt;MAX(tblData[Дата]),"",C269+1))</f>
         <v/>
       </c>
     </row>
     <row r="271">
-      <c r="C271" s="49">
+      <c r="C271" s="49" t="str">
         <f>IF(C270="","",IF(C270+1&gt;MAX(tblData[Дата]),"",C270+1))</f>
         <v/>
       </c>
     </row>
     <row r="272">
-      <c r="C272" s="49">
+      <c r="C272" s="49" t="str">
         <f>IF(C271="","",IF(C271+1&gt;MAX(tblData[Дата]),"",C271+1))</f>
         <v/>
       </c>
     </row>
     <row r="273">
-      <c r="C273" s="49">
+      <c r="C273" s="49" t="str">
         <f>IF(C272="","",IF(C272+1&gt;MAX(tblData[Дата]),"",C272+1))</f>
         <v/>
       </c>
     </row>
     <row r="274">
-      <c r="C274" s="49">
+      <c r="C274" s="49" t="str">
         <f>IF(C273="","",IF(C273+1&gt;MAX(tblData[Дата]),"",C273+1))</f>
         <v/>
       </c>
     </row>
     <row r="275">
-      <c r="C275" s="49">
+      <c r="C275" s="49" t="str">
         <f>IF(C274="","",IF(C274+1&gt;MAX(tblData[Дата]),"",C274+1))</f>
         <v/>
       </c>
     </row>
     <row r="276">
-      <c r="C276" s="49">
+      <c r="C276" s="49" t="str">
         <f>IF(C275="","",IF(C275+1&gt;MAX(tblData[Дата]),"",C275+1))</f>
         <v/>
       </c>
     </row>
     <row r="277">
-      <c r="C277" s="49">
+      <c r="C277" s="49" t="str">
         <f>IF(C276="","",IF(C276+1&gt;MAX(tblData[Дата]),"",C276+1))</f>
         <v/>
       </c>
     </row>
     <row r="278">
-      <c r="C278" s="49">
+      <c r="C278" s="49" t="str">
         <f>IF(C277="","",IF(C277+1&gt;MAX(tblData[Дата]),"",C277+1))</f>
         <v/>
       </c>
     </row>
     <row r="279">
-      <c r="C279" s="49">
+      <c r="C279" s="49" t="str">
         <f>IF(C278="","",IF(C278+1&gt;MAX(tblData[Дата]),"",C278+1))</f>
         <v/>
       </c>
     </row>
     <row r="280">
-      <c r="C280" s="49">
+      <c r="C280" s="49" t="str">
         <f>IF(C279="","",IF(C279+1&gt;MAX(tblData[Дата]),"",C279+1))</f>
         <v/>
       </c>
     </row>
     <row r="281">
-      <c r="C281" s="49">
+      <c r="C281" s="49" t="str">
         <f>IF(C280="","",IF(C280+1&gt;MAX(tblData[Дата]),"",C280+1))</f>
         <v/>
       </c>
     </row>
     <row r="282">
-      <c r="C282" s="49">
+      <c r="C282" s="49" t="str">
         <f>IF(C281="","",IF(C281+1&gt;MAX(tblData[Дата]),"",C281+1))</f>
         <v/>
       </c>
     </row>
     <row r="283">
-      <c r="C283" s="49">
+      <c r="C283" s="49" t="str">
         <f>IF(C282="","",IF(C282+1&gt;MAX(tblData[Дата]),"",C282+1))</f>
         <v/>
       </c>
     </row>
     <row r="284">
-      <c r="C284" s="49">
+      <c r="C284" s="49" t="str">
         <f>IF(C283="","",IF(C283+1&gt;MAX(tblData[Дата]),"",C283+1))</f>
         <v/>
       </c>
     </row>
     <row r="285">
-      <c r="C285" s="49">
+      <c r="C285" s="49" t="str">
         <f>IF(C284="","",IF(C284+1&gt;MAX(tblData[Дата]),"",C284+1))</f>
         <v/>
       </c>
     </row>
     <row r="286">
-      <c r="C286" s="49">
+      <c r="C286" s="49" t="str">
         <f>IF(C285="","",IF(C285+1&gt;MAX(tblData[Дата]),"",C285+1))</f>
         <v/>
       </c>
     </row>
     <row r="287">
-      <c r="C287" s="49">
+      <c r="C287" s="49" t="str">
         <f>IF(C286="","",IF(C286+1&gt;MAX(tblData[Дата]),"",C286+1))</f>
         <v/>
       </c>
     </row>
     <row r="288">
-      <c r="C288" s="49">
+      <c r="C288" s="49" t="str">
         <f>IF(C287="","",IF(C287+1&gt;MAX(tblData[Дата]),"",C287+1))</f>
         <v/>
       </c>
     </row>
     <row r="289">
-      <c r="C289" s="49">
+      <c r="C289" s="49" t="str">
         <f>IF(C288="","",IF(C288+1&gt;MAX(tblData[Дата]),"",C288+1))</f>
         <v/>
       </c>
     </row>
     <row r="290">
-      <c r="C290" s="49">
+      <c r="C290" s="49" t="str">
         <f>IF(C289="","",IF(C289+1&gt;MAX(tblData[Дата]),"",C289+1))</f>
         <v/>
       </c>
     </row>
     <row r="291">
-      <c r="C291" s="49">
+      <c r="C291" s="49" t="str">
         <f>IF(C290="","",IF(C290+1&gt;MAX(tblData[Дата]),"",C290+1))</f>
         <v/>
       </c>
     </row>
     <row r="292">
-      <c r="C292" s="49">
+      <c r="C292" s="49" t="str">
         <f>IF(C291="","",IF(C291+1&gt;MAX(tblData[Дата]),"",C291+1))</f>
         <v/>
       </c>
     </row>
     <row r="293">
-      <c r="C293" s="49">
+      <c r="C293" s="49" t="str">
         <f>IF(C292="","",IF(C292+1&gt;MAX(tblData[Дата]),"",C292+1))</f>
         <v/>
       </c>
     </row>
     <row r="294">
-      <c r="C294" s="49">
+      <c r="C294" s="49" t="str">
         <f>IF(C293="","",IF(C293+1&gt;MAX(tblData[Дата]),"",C293+1))</f>
         <v/>
       </c>
     </row>
     <row r="295">
-      <c r="C295" s="49">
+      <c r="C295" s="49" t="str">
         <f>IF(C294="","",IF(C294+1&gt;MAX(tblData[Дата]),"",C294+1))</f>
         <v/>
       </c>
     </row>
     <row r="296">
-      <c r="C296" s="49">
+      <c r="C296" s="49" t="str">
         <f>IF(C295="","",IF(C295+1&gt;MAX(tblData[Дата]),"",C295+1))</f>
         <v/>
       </c>
     </row>
     <row r="297">
-      <c r="C297" s="49">
+      <c r="C297" s="49" t="str">
         <f>IF(C296="","",IF(C296+1&gt;MAX(tblData[Дата]),"",C296+1))</f>
         <v/>
       </c>
     </row>
     <row r="298">
-      <c r="C298" s="49">
+      <c r="C298" s="49" t="str">
         <f>IF(C297="","",IF(C297+1&gt;MAX(tblData[Дата]),"",C297+1))</f>
         <v/>
       </c>
     </row>
     <row r="299">
-      <c r="C299" s="49">
+      <c r="C299" s="49" t="str">
         <f>IF(C298="","",IF(C298+1&gt;MAX(tblData[Дата]),"",C298+1))</f>
         <v/>
       </c>
     </row>
     <row r="300">
-      <c r="C300" s="49">
+      <c r="C300" s="49" t="str">
         <f>IF(C299="","",IF(C299+1&gt;MAX(tblData[Дата]),"",C299+1))</f>
         <v/>
       </c>
     </row>
     <row r="301">
-      <c r="C301" s="49">
+      <c r="C301" s="49" t="str">
         <f>IF(C300="","",IF(C300+1&gt;MAX(tblData[Дата]),"",C300+1))</f>
         <v/>
       </c>
     </row>
     <row r="302">
-      <c r="C302" s="49">
+      <c r="C302" s="49" t="str">
         <f>IF(C301="","",IF(C301+1&gt;MAX(tblData[Дата]),"",C301+1))</f>
         <v/>
       </c>
     </row>
     <row r="303">
-      <c r="C303" s="49">
+      <c r="C303" s="49" t="str">
         <f>IF(C302="","",IF(C302+1&gt;MAX(tblData[Дата]),"",C302+1))</f>
         <v/>
       </c>
     </row>
     <row r="304">
-      <c r="C304" s="49">
+      <c r="C304" s="49" t="str">
         <f>IF(C303="","",IF(C303+1&gt;MAX(tblData[Дата]),"",C303+1))</f>
         <v/>
       </c>
     </row>
     <row r="305">
-      <c r="C305" s="49">
+      <c r="C305" s="49" t="str">
         <f>IF(C304="","",IF(C304+1&gt;MAX(tblData[Дата]),"",C304+1))</f>
         <v/>
       </c>
     </row>
     <row r="306">
-      <c r="C306" s="49">
+      <c r="C306" s="49" t="str">
         <f>IF(C305="","",IF(C305+1&gt;MAX(tblData[Дата]),"",C305+1))</f>
         <v/>
       </c>
     </row>
     <row r="307">
-      <c r="C307" s="49">
+      <c r="C307" s="49" t="str">
         <f>IF(C306="","",IF(C306+1&gt;MAX(tblData[Дата]),"",C306+1))</f>
         <v/>
       </c>
     </row>
     <row r="308">
-      <c r="C308" s="49">
+      <c r="C308" s="49" t="str">
         <f>IF(C307="","",IF(C307+1&gt;MAX(tblData[Дата]),"",C307+1))</f>
         <v/>
       </c>
     </row>
     <row r="309">
-      <c r="C309" s="49">
+      <c r="C309" s="49" t="str">
         <f>IF(C308="","",IF(C308+1&gt;MAX(tblData[Дата]),"",C308+1))</f>
         <v/>
       </c>
     </row>
     <row r="310">
-      <c r="C310" s="49">
+      <c r="C310" s="49" t="str">
         <f>IF(C309="","",IF(C309+1&gt;MAX(tblData[Дата]),"",C309+1))</f>
         <v/>
       </c>
     </row>
     <row r="311">
-      <c r="C311" s="49">
+      <c r="C311" s="49" t="str">
         <f>IF(C310="","",IF(C310+1&gt;MAX(tblData[Дата]),"",C310+1))</f>
         <v/>
       </c>
     </row>
     <row r="312">
-      <c r="C312" s="49">
+      <c r="C312" s="49" t="str">
         <f>IF(C311="","",IF(C311+1&gt;MAX(tblData[Дата]),"",C311+1))</f>
         <v/>
       </c>
     </row>
     <row r="313">
-      <c r="C313" s="49">
+      <c r="C313" s="49" t="str">
         <f>IF(C312="","",IF(C312+1&gt;MAX(tblData[Дата]),"",C312+1))</f>
         <v/>
       </c>
     </row>
     <row r="314">
-      <c r="C314" s="49">
+      <c r="C314" s="49" t="str">
         <f>IF(C313="","",IF(C313+1&gt;MAX(tblData[Дата]),"",C313+1))</f>
         <v/>
       </c>
     </row>
     <row r="315">
-      <c r="C315" s="49">
+      <c r="C315" s="49" t="str">
         <f>IF(C314="","",IF(C314+1&gt;MAX(tblData[Дата]),"",C314+1))</f>
         <v/>
       </c>
     </row>
     <row r="316">
-      <c r="C316" s="49">
+      <c r="C316" s="49" t="str">
         <f>IF(C315="","",IF(C315+1&gt;MAX(tblData[Дата]),"",C315+1))</f>
         <v/>
       </c>
     </row>
     <row r="317">
-      <c r="C317" s="49">
+      <c r="C317" s="49" t="str">
         <f>IF(C316="","",IF(C316+1&gt;MAX(tblData[Дата]),"",C316+1))</f>
         <v/>
       </c>
     </row>
     <row r="318">
-      <c r="C318" s="49">
+      <c r="C318" s="49" t="str">
         <f>IF(C317="","",IF(C317+1&gt;MAX(tblData[Дата]),"",C317+1))</f>
         <v/>
       </c>
     </row>
     <row r="319">
-      <c r="C319" s="49">
+      <c r="C319" s="49" t="str">
         <f>IF(C318="","",IF(C318+1&gt;MAX(tblData[Дата]),"",C318+1))</f>
         <v/>
       </c>
     </row>
     <row r="320">
-      <c r="C320" s="49">
+      <c r="C320" s="49" t="str">
         <f>IF(C319="","",IF(C319+1&gt;MAX(tblData[Дата]),"",C319+1))</f>
         <v/>
       </c>
     </row>
     <row r="321">
-      <c r="C321" s="49">
+      <c r="C321" s="49" t="str">
         <f>IF(C320="","",IF(C320+1&gt;MAX(tblData[Дата]),"",C320+1))</f>
         <v/>
       </c>
     </row>
     <row r="322">
-      <c r="C322" s="49">
+      <c r="C322" s="49" t="str">
         <f>IF(C321="","",IF(C321+1&gt;MAX(tblData[Дата]),"",C321+1))</f>
         <v/>
       </c>
     </row>
     <row r="323">
-      <c r="C323" s="49">
+      <c r="C323" s="49" t="str">
         <f>IF(C322="","",IF(C322+1&gt;MAX(tblData[Дата]),"",C322+1))</f>
         <v/>
       </c>
     </row>
     <row r="324">
-      <c r="C324" s="49">
+      <c r="C324" s="49" t="str">
         <f>IF(C323="","",IF(C323+1&gt;MAX(tblData[Дата]),"",C323+1))</f>
         <v/>
       </c>
     </row>
     <row r="325">
-      <c r="C325" s="49">
+      <c r="C325" s="49" t="str">
         <f>IF(C324="","",IF(C324+1&gt;MAX(tblData[Дата]),"",C324+1))</f>
         <v/>
       </c>
     </row>
     <row r="326">
-      <c r="C326" s="49">
+      <c r="C326" s="49" t="str">
         <f>IF(C325="","",IF(C325+1&gt;MAX(tblData[Дата]),"",C325+1))</f>
         <v/>
       </c>
     </row>
     <row r="327">
-      <c r="C327" s="49">
+      <c r="C327" s="49" t="str">
         <f>IF(C326="","",IF(C326+1&gt;MAX(tblData[Дата]),"",C326+1))</f>
         <v/>
       </c>
     </row>
     <row r="328">
-      <c r="C328" s="49">
+      <c r="C328" s="49" t="str">
         <f>IF(C327="","",IF(C327+1&gt;MAX(tblData[Дата]),"",C327+1))</f>
         <v/>
       </c>
     </row>
     <row r="329">
-      <c r="C329" s="49">
+      <c r="C329" s="49" t="str">
         <f>IF(C328="","",IF(C328+1&gt;MAX(tblData[Дата]),"",C328+1))</f>
         <v/>
       </c>
     </row>
     <row r="330">
-      <c r="C330" s="49">
+      <c r="C330" s="49" t="str">
         <f>IF(C329="","",IF(C329+1&gt;MAX(tblData[Дата]),"",C329+1))</f>
         <v/>
       </c>
     </row>
     <row r="331">
-      <c r="C331" s="49">
+      <c r="C331" s="49" t="str">
         <f>IF(C330="","",IF(C330+1&gt;MAX(tblData[Дата]),"",C330+1))</f>
         <v/>
       </c>
     </row>
     <row r="332">
-      <c r="C332" s="49">
+      <c r="C332" s="49" t="str">
         <f>IF(C331="","",IF(C331+1&gt;MAX(tblData[Дата]),"",C331+1))</f>
         <v/>
       </c>
     </row>
     <row r="333">
-      <c r="C333" s="49">
+      <c r="C333" s="49" t="str">
         <f>IF(C332="","",IF(C332+1&gt;MAX(tblData[Дата]),"",C332+1))</f>
         <v/>
       </c>
     </row>
     <row r="334">
-      <c r="C334" s="49">
+      <c r="C334" s="49" t="str">
         <f>IF(C333="","",IF(C333+1&gt;MAX(tblData[Дата]),"",C333+1))</f>
         <v/>
       </c>
     </row>
     <row r="335">
-      <c r="C335" s="49">
+      <c r="C335" s="49" t="str">
         <f>IF(C334="","",IF(C334+1&gt;MAX(tblData[Дата]),"",C334+1))</f>
         <v/>
       </c>
     </row>
     <row r="336">
-      <c r="C336" s="49">
+      <c r="C336" s="49" t="str">
         <f>IF(C335="","",IF(C335+1&gt;MAX(tblData[Дата]),"",C335+1))</f>
         <v/>
       </c>
     </row>
     <row r="337">
-      <c r="C337" s="49">
+      <c r="C337" s="49" t="str">
         <f>IF(C336="","",IF(C336+1&gt;MAX(tblData[Дата]),"",C336+1))</f>
         <v/>
       </c>
     </row>
     <row r="338">
-      <c r="C338" s="49">
+      <c r="C338" s="49" t="str">
         <f>IF(C337="","",IF(C337+1&gt;MAX(tblData[Дата]),"",C337+1))</f>
         <v/>
       </c>
     </row>
     <row r="339">
-      <c r="C339" s="49">
+      <c r="C339" s="49" t="str">
         <f>IF(C338="","",IF(C338+1&gt;MAX(tblData[Дата]),"",C338+1))</f>
         <v/>
       </c>
     </row>
     <row r="340">
-      <c r="C340" s="49">
+      <c r="C340" s="49" t="str">
         <f>IF(C339="","",IF(C339+1&gt;MAX(tblData[Дата]),"",C339+1))</f>
         <v/>
       </c>
     </row>
     <row r="341">
-      <c r="C341" s="49">
+      <c r="C341" s="49" t="str">
         <f>IF(C340="","",IF(C340+1&gt;MAX(tblData[Дата]),"",C340+1))</f>
         <v/>
       </c>
     </row>
     <row r="342">
-      <c r="C342" s="49">
+      <c r="C342" s="49" t="str">
         <f>IF(C341="","",IF(C341+1&gt;MAX(tblData[Дата]),"",C341+1))</f>
         <v/>
       </c>
     </row>
     <row r="343">
-      <c r="C343" s="49">
+      <c r="C343" s="49" t="str">
         <f>IF(C342="","",IF(C342+1&gt;MAX(tblData[Дата]),"",C342+1))</f>
         <v/>
       </c>
     </row>
     <row r="344">
-      <c r="C344" s="49">
+      <c r="C344" s="49" t="str">
         <f>IF(C343="","",IF(C343+1&gt;MAX(tblData[Дата]),"",C343+1))</f>
         <v/>
       </c>
     </row>
     <row r="345">
-      <c r="C345" s="49">
+      <c r="C345" s="49" t="str">
         <f>IF(C344="","",IF(C344+1&gt;MAX(tblData[Дата]),"",C344+1))</f>
         <v/>
       </c>
     </row>
     <row r="346">
-      <c r="C346" s="49">
+      <c r="C346" s="49" t="str">
         <f>IF(C345="","",IF(C345+1&gt;MAX(tblData[Дата]),"",C345+1))</f>
         <v/>
       </c>
     </row>
     <row r="347">
-      <c r="C347" s="49">
+      <c r="C347" s="49" t="str">
         <f>IF(C346="","",IF(C346+1&gt;MAX(tblData[Дата]),"",C346+1))</f>
         <v/>
       </c>
     </row>
     <row r="348">
-      <c r="C348" s="49">
+      <c r="C348" s="49" t="str">
         <f>IF(C347="","",IF(C347+1&gt;MAX(tblData[Дата]),"",C347+1))</f>
         <v/>
       </c>
     </row>
     <row r="349">
-      <c r="C349" s="49">
+      <c r="C349" s="49" t="str">
         <f>IF(C348="","",IF(C348+1&gt;MAX(tblData[Дата]),"",C348+1))</f>
         <v/>
       </c>
     </row>
     <row r="350">
-      <c r="C350" s="49">
+      <c r="C350" s="49" t="str">
         <f>IF(C349="","",IF(C349+1&gt;MAX(tblData[Дата]),"",C349+1))</f>
         <v/>
       </c>
     </row>
     <row r="351">
-      <c r="C351" s="49">
+      <c r="C351" s="49" t="str">
         <f>IF(C350="","",IF(C350+1&gt;MAX(tblData[Дата]),"",C350+1))</f>
         <v/>
       </c>
     </row>
     <row r="352">
-      <c r="C352" s="49">
+      <c r="C352" s="49" t="str">
         <f>IF(C351="","",IF(C351+1&gt;MAX(tblData[Дата]),"",C351+1))</f>
         <v/>
       </c>
     </row>
     <row r="353">
-      <c r="C353" s="49">
+      <c r="C353" s="49" t="str">
         <f>IF(C352="","",IF(C352+1&gt;MAX(tblData[Дата]),"",C352+1))</f>
         <v/>
       </c>
     </row>
     <row r="354">
-      <c r="C354" s="49">
+      <c r="C354" s="49" t="str">
         <f>IF(C353="","",IF(C353+1&gt;MAX(tblData[Дата]),"",C353+1))</f>
         <v/>
       </c>
     </row>
     <row r="355">
-      <c r="C355" s="49">
+      <c r="C355" s="49" t="str">
         <f>IF(C354="","",IF(C354+1&gt;MAX(tblData[Дата]),"",C354+1))</f>
         <v/>
       </c>
     </row>
     <row r="356">
-      <c r="C356" s="49">
+      <c r="C356" s="49" t="str">
         <f>IF(C355="","",IF(C355+1&gt;MAX(tblData[Дата]),"",C355+1))</f>
         <v/>
       </c>
     </row>
     <row r="357">
-      <c r="C357" s="49">
+      <c r="C357" s="49" t="str">
         <f>IF(C356="","",IF(C356+1&gt;MAX(tblData[Дата]),"",C356+1))</f>
         <v/>
       </c>
     </row>
     <row r="358">
-      <c r="C358" s="49">
+      <c r="C358" s="49" t="str">
         <f>IF(C357="","",IF(C357+1&gt;MAX(tblData[Дата]),"",C357+1))</f>
         <v/>
       </c>
     </row>
     <row r="359">
-      <c r="C359" s="49">
+      <c r="C359" s="49" t="str">
         <f>IF(C358="","",IF(C358+1&gt;MAX(tblData[Дата]),"",C358+1))</f>
         <v/>
       </c>
     </row>
     <row r="360">
-      <c r="C360" s="49">
+      <c r="C360" s="49" t="str">
         <f>IF(C359="","",IF(C359+1&gt;MAX(tblData[Дата]),"",C359+1))</f>
         <v/>
       </c>
     </row>
     <row r="361">
-      <c r="C361" s="49">
+      <c r="C361" s="49" t="str">
         <f>IF(C360="","",IF(C360+1&gt;MAX(tblData[Дата]),"",C360+1))</f>
         <v/>
       </c>
     </row>
     <row r="362">
-      <c r="C362" s="49">
+      <c r="C362" s="49" t="str">
         <f>IF(C361="","",IF(C361+1&gt;MAX(tblData[Дата]),"",C361+1))</f>
         <v/>
       </c>
     </row>
     <row r="363">
-      <c r="C363" s="49">
+      <c r="C363" s="49" t="str">
         <f>IF(C362="","",IF(C362+1&gt;MAX(tblData[Дата]),"",C362+1))</f>
         <v/>
       </c>
     </row>
     <row r="364">
-      <c r="C364" s="49">
+      <c r="C364" s="49" t="str">
         <f>IF(C363="","",IF(C363+1&gt;MAX(tblData[Дата]),"",C363+1))</f>
         <v/>
       </c>
     </row>
     <row r="365">
-      <c r="C365" s="49">
+      <c r="C365" s="49" t="str">
         <f>IF(C364="","",IF(C364+1&gt;MAX(tblData[Дата]),"",C364+1))</f>
         <v/>
       </c>
     </row>
     <row r="366">
-      <c r="C366" s="49">
+      <c r="C366" s="49" t="str">
         <f>IF(C365="","",IF(C365+1&gt;MAX(tblData[Дата]),"",C365+1))</f>
         <v/>
       </c>
     </row>
     <row r="367">
-      <c r="C367" s="49">
+      <c r="C367" s="49" t="str">
         <f>IF(C366="","",IF(C366+1&gt;MAX(tblData[Дата]),"",C366+1))</f>
         <v/>
       </c>
     </row>
     <row r="368">
-      <c r="C368" s="49">
+      <c r="C368" s="49" t="str">
         <f>IF(C367="","",IF(C367+1&gt;MAX(tblData[Дата]),"",C367+1))</f>
         <v/>
       </c>
     </row>
     <row r="369">
-      <c r="C369" s="49">
+      <c r="C369" s="49" t="str">
         <f>IF(C368="","",IF(C368+1&gt;MAX(tblData[Дата]),"",C368+1))</f>
         <v/>
       </c>
     </row>
     <row r="370">
-      <c r="C370" s="49">
+      <c r="C370" s="49" t="str">
         <f>IF(C369="","",IF(C369+1&gt;MAX(tblData[Дата]),"",C369+1))</f>
         <v/>
       </c>
     </row>
     <row r="371">
-      <c r="C371" s="49">
+      <c r="C371" s="49" t="str">
         <f>IF(C370="","",IF(C370+1&gt;MAX(tblData[Дата]),"",C370+1))</f>
         <v/>
       </c>
     </row>
     <row r="372">
-      <c r="C372" s="49">
+      <c r="C372" s="49" t="str">
         <f>IF(C371="","",IF(C371+1&gt;MAX(tblData[Дата]),"",C371+1))</f>
         <v/>
       </c>
     </row>
     <row r="373">
-      <c r="C373" s="49">
+      <c r="C373" s="49" t="str">
         <f>IF(C372="","",IF(C372+1&gt;MAX(tblData[Дата]),"",C372+1))</f>
         <v/>
       </c>
     </row>
     <row r="374">
-      <c r="C374" s="49">
+      <c r="C374" s="49" t="str">
         <f>IF(C373="","",IF(C373+1&gt;MAX(tblData[Дата]),"",C373+1))</f>
         <v/>
       </c>
     </row>
     <row r="375">
-      <c r="C375" s="49">
+      <c r="C375" s="49" t="str">
         <f>IF(C374="","",IF(C374+1&gt;MAX(tblData[Дата]),"",C374+1))</f>
         <v/>
       </c>
     </row>
     <row r="376">
-      <c r="C376" s="49">
+      <c r="C376" s="49" t="str">
         <f>IF(C375="","",IF(C375+1&gt;MAX(tblData[Дата]),"",C375+1))</f>
         <v/>
       </c>
     </row>
     <row r="377">
-      <c r="C377" s="49">
+      <c r="C377" s="49" t="str">
         <f>IF(C376="","",IF(C376+1&gt;MAX(tblData[Дата]),"",C376+1))</f>
         <v/>
       </c>
     </row>
     <row r="378">
-      <c r="C378" s="49">
+      <c r="C378" s="49" t="str">
         <f>IF(C377="","",IF(C377+1&gt;MAX(tblData[Дата]),"",C377+1))</f>
         <v/>
       </c>
     </row>
     <row r="379">
-      <c r="C379" s="49">
+      <c r="C379" s="49" t="str">
         <f>IF(C378="","",IF(C378+1&gt;MAX(tblData[Дата]),"",C378+1))</f>
         <v/>
       </c>
     </row>
     <row r="380">
-      <c r="C380" s="49">
+      <c r="C380" s="49" t="str">
         <f>IF(C379="","",IF(C379+1&gt;MAX(tblData[Дата]),"",C379+1))</f>
         <v/>
       </c>
     </row>
     <row r="381">
-      <c r="C381" s="49">
+      <c r="C381" s="49" t="str">
         <f>IF(C380="","",IF(C380+1&gt;MAX(tblData[Дата]),"",C380+1))</f>
         <v/>
       </c>
     </row>
     <row r="382">
-      <c r="C382" s="49">
+      <c r="C382" s="49" t="str">
         <f>IF(C381="","",IF(C381+1&gt;MAX(tblData[Дата]),"",C381+1))</f>
         <v/>
       </c>
     </row>
     <row r="383">
-      <c r="C383" s="49">
+      <c r="C383" s="49" t="str">
         <f>IF(C382="","",IF(C382+1&gt;MAX(tblData[Дата]),"",C382+1))</f>
         <v/>
       </c>
     </row>
     <row r="384">
-      <c r="C384" s="49">
+      <c r="C384" s="49" t="str">
         <f>IF(C383="","",IF(C383+1&gt;MAX(tblData[Дата]),"",C383+1))</f>
         <v/>
       </c>
     </row>
     <row r="385">
-      <c r="C385" s="49">
+      <c r="C385" s="49" t="str">
         <f>IF(C384="","",IF(C384+1&gt;MAX(tblData[Дата]),"",C384+1))</f>
         <v/>
       </c>
     </row>
     <row r="386">
-      <c r="C386" s="49">
+      <c r="C386" s="49" t="str">
         <f>IF(C385="","",IF(C385+1&gt;MAX(tblData[Дата]),"",C385+1))</f>
         <v/>
       </c>
     </row>
     <row r="387">
-      <c r="C387" s="49">
+      <c r="C387" s="49" t="str">
         <f>IF(C386="","",IF(C386+1&gt;MAX(tblData[Дата]),"",C386+1))</f>
         <v/>
       </c>
     </row>
     <row r="388">
-      <c r="C388" s="49">
+      <c r="C388" s="49" t="str">
         <f>IF(C387="","",IF(C387+1&gt;MAX(tblData[Дата]),"",C387+1))</f>
         <v/>
       </c>
     </row>
     <row r="389">
-      <c r="C389" s="49">
+      <c r="C389" s="49" t="str">
         <f>IF(C388="","",IF(C388+1&gt;MAX(tblData[Дата]),"",C388+1))</f>
         <v/>
       </c>
     </row>
     <row r="390">
-      <c r="C390" s="49">
+      <c r="C390" s="49" t="str">
         <f>IF(C389="","",IF(C389+1&gt;MAX(tblData[Дата]),"",C389+1))</f>
         <v/>
       </c>
     </row>
     <row r="391">
-      <c r="C391" s="49">
+      <c r="C391" s="49" t="str">
         <f>IF(C390="","",IF(C390+1&gt;MAX(tblData[Дата]),"",C390+1))</f>
         <v/>
       </c>
     </row>
     <row r="392">
-      <c r="C392" s="49">
+      <c r="C392" s="49" t="str">
         <f>IF(C391="","",IF(C391+1&gt;MAX(tblData[Дата]),"",C391+1))</f>
         <v/>
       </c>
     </row>
     <row r="393">
-      <c r="C393" s="49">
+      <c r="C393" s="49" t="str">
         <f>IF(C392="","",IF(C392+1&gt;MAX(tblData[Дата]),"",C392+1))</f>
         <v/>
       </c>
     </row>
     <row r="394">
-      <c r="C394" s="49">
+      <c r="C394" s="49" t="str">
         <f>IF(C393="","",IF(C393+1&gt;MAX(tblData[Дата]),"",C393+1))</f>
         <v/>
       </c>
     </row>
     <row r="395">
-      <c r="C395" s="49">
+      <c r="C395" s="49" t="str">
         <f>IF(C394="","",IF(C394+1&gt;MAX(tblData[Дата]),"",C394+1))</f>
         <v/>
       </c>
     </row>
     <row r="396">
-      <c r="C396" s="49">
+      <c r="C396" s="49" t="str">
         <f>IF(C395="","",IF(C395+1&gt;MAX(tblData[Дата]),"",C395+1))</f>
         <v/>
       </c>
     </row>
     <row r="397">
-      <c r="C397" s="49">
+      <c r="C397" s="49" t="str">
         <f>IF(C396="","",IF(C396+1&gt;MAX(tblData[Дата]),"",C396+1))</f>
         <v/>
       </c>
     </row>
     <row r="398">
-      <c r="C398" s="49">
+      <c r="C398" s="49" t="str">
         <f>IF(C397="","",IF(C397+1&gt;MAX(tblData[Дата]),"",C397+1))</f>
         <v/>
       </c>
     </row>
     <row r="399">
-      <c r="C399" s="49">
+      <c r="C399" s="49" t="str">
         <f>IF(C398="","",IF(C398+1&gt;MAX(tblData[Дата]),"",C398+1))</f>
         <v/>
       </c>
     </row>
     <row r="400">
-      <c r="C400" s="49">
+      <c r="C400" s="49" t="str">
         <f>IF(C399="","",IF(C399+1&gt;MAX(tblData[Дата]),"",C399+1))</f>
         <v/>
       </c>
     </row>
     <row r="401">
-      <c r="C401" s="49">
+      <c r="C401" s="49" t="str">
         <f>IF(C400="","",IF(C400+1&gt;MAX(tblData[Дата]),"",C400+1))</f>
         <v/>
       </c>
